--- a/example data/5mm/Results/ID 15 - Run 3/ID 15 - Run 3 - Normalised Stepcycles.xlsx
+++ b/example data/5mm/Results/ID 15 - Run 3/ID 15 - Run 3 - Normalised Stepcycles.xlsx
@@ -666,67 +666,67 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
+          <t>Hind paw tao Velocity</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Acceleration</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Velocity</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Acceleration</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Velocity</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Acceleration</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Velocity</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Acceleration</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Velocity</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Acceleration</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
           <t>Ankle Angle</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Velocity</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Acceleration</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Velocity</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Acceleration</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Velocity</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Acceleration</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Velocity</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Acceleration</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Velocity</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Acceleration</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
@@ -768,43 +768,43 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>122.4789112172228</v>
+        <v>86.60520188351896</v>
       </c>
       <c r="D2" t="n">
-        <v>3.280590950174528</v>
+        <v>3.280590950174535</v>
       </c>
       <c r="E2" t="n">
         <v>0.9995053708553314</v>
       </c>
       <c r="F2" t="n">
-        <v>105.3659926069544</v>
+        <v>69.49228327325051</v>
       </c>
       <c r="G2" t="n">
-        <v>13.46892498909158</v>
+        <v>13.46892498909159</v>
       </c>
       <c r="H2" t="n">
         <v>0.9993174374103546</v>
       </c>
       <c r="I2" t="n">
-        <v>87.55972030314993</v>
+        <v>51.68601096944607</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1887707000083196</v>
+        <v>-0.1887707000083112</v>
       </c>
       <c r="K2" t="n">
         <v>0.9990449845790863</v>
       </c>
       <c r="L2" t="n">
-        <v>84.03644967586436</v>
+        <v>48.16274034216049</v>
       </c>
       <c r="M2" t="n">
-        <v>3.006565824468069</v>
+        <v>3.006565824468085</v>
       </c>
       <c r="N2" t="n">
         <v>0.9994745552539825</v>
       </c>
       <c r="O2" t="n">
-        <v>83.3868554297914</v>
+        <v>47.51314609608752</v>
       </c>
       <c r="P2" t="n">
         <v>12.71490543446642</v>
@@ -813,7 +813,7 @@
         <v>0.9650624394416809</v>
       </c>
       <c r="R2" t="n">
-        <v>92.95093049394325</v>
+        <v>57.07722116023937</v>
       </c>
       <c r="S2" t="n">
         <v>15.36267057378241</v>
@@ -822,7 +822,7 @@
         <v>0.9891234934329987</v>
       </c>
       <c r="U2" t="n">
-        <v>90.06891047700923</v>
+        <v>54.19520114330535</v>
       </c>
       <c r="V2" t="n">
         <v>24.52437624018243</v>
@@ -831,25 +831,25 @@
         <v>0.9784575998783112</v>
       </c>
       <c r="X2" t="n">
-        <v>47.43531206820874</v>
+        <v>11.56160273450487</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.07961467986412</v>
+        <v>27.07961467986411</v>
       </c>
       <c r="Z2" t="n">
         <v>0.9914674460887909</v>
       </c>
       <c r="AA2" t="n">
-        <v>42.73586273193359</v>
+        <v>6.862153398229726</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.21682154878658</v>
+        <v>19.21682154878657</v>
       </c>
       <c r="AC2" t="n">
         <v>0.9959852695465088</v>
       </c>
       <c r="AD2" t="n">
-        <v>47.83291309437854</v>
+        <v>11.95920376067467</v>
       </c>
       <c r="AE2" t="n">
         <v>12.31073420098488</v>
@@ -858,7 +858,7 @@
         <v>0.9774917364120483</v>
       </c>
       <c r="AG2" t="n">
-        <v>36.59742639419881</v>
+        <v>0.7237170604949341</v>
       </c>
       <c r="AH2" t="n">
         <v>9.680557250976562</v>
@@ -867,97 +867,97 @@
         <v>0.998733788728714</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40.13380091241066</v>
+        <v>4.260091578706785</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.6188088275016526</v>
+        <v>-0.6188088275016622</v>
       </c>
       <c r="AL2" t="n">
         <v>0.9982028305530548</v>
       </c>
       <c r="AM2" t="n">
-        <v>31.41544829023645</v>
+        <v>-4.458261043467417</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.25020648063497</v>
+        <v>23.25020648063498</v>
       </c>
       <c r="AO2" t="n">
         <v>0.9995947182178497</v>
       </c>
       <c r="AP2" t="n">
-        <v>16.72059120015895</v>
+        <v>-19.15311813354492</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28.75330093059135</v>
+        <v>28.75330093059134</v>
       </c>
       <c r="AR2" t="n">
         <v>0.8939022719860077</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.957225150250375</v>
+        <v>-27.9164841834535</v>
       </c>
       <c r="AT2" t="n">
-        <v>17.4475243751039</v>
+        <v>17.44752437510389</v>
       </c>
       <c r="AU2" t="n">
         <v>0.364995926618576</v>
       </c>
       <c r="AV2" t="n">
-        <v>84.21855210885917</v>
+        <v>8.629482350450886</v>
       </c>
       <c r="AW2" t="n">
-        <v>66.29740300938886</v>
+        <v>0.2786768243667899</v>
       </c>
       <c r="AX2" t="n">
-        <v>112.4594662487496</v>
+        <v>4.727318946351398</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.629482350450886</v>
+        <v>1.168027329952157</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2786768243667899</v>
+        <v>3.739480769380609</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.727318946351398</v>
+        <v>-0.108800035841921</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.168027329952157</v>
+        <v>1.690192932778213</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.739480769380609</v>
+        <v>0.09922727625421057</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.108800035841921</v>
+        <v>1.464373000124667</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.690192932778213</v>
+        <v>-0.08742251294724301</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.09922727625421057</v>
+        <v>84.21855210885916</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.464373000124667</v>
+        <v>66.29740300938877</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.08742251294724301</v>
+        <v>112.4594662487495</v>
       </c>
       <c r="BI2" t="n">
-        <v>-2.937543965034138</v>
+        <v>-2.937543965034063</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.025087971937634</v>
+        <v>1.025087971937571</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.405594002015597</v>
+        <v>1.405594002015622</v>
       </c>
       <c r="BL2" t="n">
-        <v>3.437327204491636</v>
+        <v>3.437327204491673</v>
       </c>
       <c r="BM2" t="n">
         <v>-16.06464850287235</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.96499330245017</v>
+        <v>3.964993302450138</v>
       </c>
     </row>
     <row r="3">
@@ -968,79 +968,79 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>124.2222481585564</v>
+        <v>88.34853882485248</v>
       </c>
       <c r="D3" t="n">
-        <v>2.565805962745188</v>
+        <v>2.56580596274518</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999018311500549</v>
       </c>
       <c r="F3" t="n">
-        <v>106.9879004295836</v>
+        <v>71.11419109587975</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66469752534906</v>
+        <v>12.66469752534907</v>
       </c>
       <c r="H3" t="n">
         <v>0.9994963109493256</v>
       </c>
       <c r="I3" t="n">
-        <v>87.58799370298995</v>
+        <v>51.71428436928608</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3669251786901526</v>
+        <v>-0.3669251786901596</v>
       </c>
       <c r="K3" t="n">
         <v>0.999042421579361</v>
       </c>
       <c r="L3" t="n">
-        <v>84.47366673895654</v>
+        <v>48.59995740525267</v>
       </c>
       <c r="M3" t="n">
-        <v>2.839636295399771</v>
+        <v>2.839636295399767</v>
       </c>
       <c r="N3" t="n">
         <v>0.9994050264358521</v>
       </c>
       <c r="O3" t="n">
-        <v>84.81112541036404</v>
+        <v>48.93741607666016</v>
       </c>
       <c r="P3" t="n">
-        <v>12.27956731268699</v>
+        <v>12.279567312687</v>
       </c>
       <c r="Q3" t="n">
         <v>0.95342156291008</v>
       </c>
       <c r="R3" t="n">
-        <v>94.6657343113676</v>
+        <v>58.79202497766374</v>
       </c>
       <c r="S3" t="n">
-        <v>14.83836072556515</v>
+        <v>14.83836072556516</v>
       </c>
       <c r="T3" t="n">
         <v>0.9883201420307159</v>
       </c>
       <c r="U3" t="n">
-        <v>91.94344865514877</v>
+        <v>56.0697393214449</v>
       </c>
       <c r="V3" t="n">
-        <v>24.09583558427526</v>
+        <v>24.09583558427527</v>
       </c>
       <c r="W3" t="n">
         <v>0.9698670506477356</v>
       </c>
       <c r="X3" t="n">
-        <v>50.49467898429708</v>
+        <v>14.62096965059321</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.01423985907373</v>
+        <v>28.01423985907372</v>
       </c>
       <c r="Z3" t="n">
         <v>0.9920289218425751</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.50738695834546</v>
+        <v>10.63367762464159</v>
       </c>
       <c r="AB3" t="n">
         <v>19.24574020061087</v>
@@ -1049,7 +1049,7 @@
         <v>0.9950328767299652</v>
       </c>
       <c r="AD3" t="n">
-        <v>55.01639792259704</v>
+        <v>19.14268858889317</v>
       </c>
       <c r="AE3" t="n">
         <v>15.33034304355053</v>
@@ -1058,25 +1058,25 @@
         <v>0.9961864352226257</v>
       </c>
       <c r="AG3" t="n">
-        <v>48.63381690167367</v>
+        <v>12.76010756796979</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.989715900826965</v>
+        <v>5.989715900826962</v>
       </c>
       <c r="AI3" t="n">
         <v>0.9980344474315643</v>
       </c>
       <c r="AJ3" t="n">
-        <v>58.07027613863032</v>
+        <v>22.19656680492645</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.266227884495507</v>
+        <v>1.266227884495512</v>
       </c>
       <c r="AL3" t="n">
         <v>0.9973703324794769</v>
       </c>
       <c r="AM3" t="n">
-        <v>33.56053677011044</v>
+        <v>-2.313172563593433</v>
       </c>
       <c r="AN3" t="n">
         <v>23.50284495252244</v>
@@ -1085,79 +1085,79 @@
         <v>0.9993810951709747</v>
       </c>
       <c r="AP3" t="n">
-        <v>21.62796588654214</v>
+        <v>-14.24574344716173</v>
       </c>
       <c r="AQ3" t="n">
-        <v>28.85420778964429</v>
+        <v>28.85420778964428</v>
       </c>
       <c r="AR3" t="n">
         <v>0.9107633233070374</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.351703582926</v>
+        <v>-24.52200575077787</v>
       </c>
       <c r="AT3" t="n">
-        <v>16.37377637497923</v>
+        <v>16.37377637497922</v>
       </c>
       <c r="AU3" t="n">
         <v>0.9305253326892853</v>
       </c>
       <c r="AV3" t="n">
-        <v>82.10810594823653</v>
+        <v>8.803242825447244</v>
       </c>
       <c r="AW3" t="n">
-        <v>80.11042695928174</v>
+        <v>-1.062880171106217</v>
       </c>
       <c r="AX3" t="n">
-        <v>90.29962679488523</v>
+        <v>6.889570520279257</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.803242825447244</v>
+        <v>0.05029718926612414</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1.062880171106217</v>
+        <v>3.333892213537338</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.889570520279257</v>
+        <v>-0.4486824603790929</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.05029718926612414</v>
+        <v>2.306746421976293</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.333892213537338</v>
+        <v>0.08580228115649913</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.4486824603790929</v>
+        <v>1.94545197994151</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.306746421976293</v>
+        <v>0.1344630058775564</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.08580228115649913</v>
+        <v>82.1081059482365</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.94545197994151</v>
+        <v>80.11042695928177</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1344630058775564</v>
+        <v>90.2996267948852</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.45068584871084</v>
+        <v>5.450685848710787</v>
       </c>
       <c r="BJ3" t="n">
-        <v>6.716319603587941</v>
+        <v>6.716319603587943</v>
       </c>
       <c r="BK3" t="n">
-        <v>14.80534131499207</v>
+        <v>14.80534131499211</v>
       </c>
       <c r="BL3" t="n">
-        <v>3.896781925203518</v>
+        <v>3.896781925203497</v>
       </c>
       <c r="BM3" t="n">
-        <v>-4.558785226781758</v>
+        <v>-4.558785226781723</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.567692309689138</v>
+        <v>4.567692309689154</v>
       </c>
     </row>
     <row r="4">
@@ -1168,43 +1168,43 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>126.3939309627452</v>
+        <v>90.52022162904132</v>
       </c>
       <c r="D4" t="n">
-        <v>3.027603474069153</v>
+        <v>3.027603474069149</v>
       </c>
       <c r="E4" t="n">
         <v>0.9995964169502258</v>
       </c>
       <c r="F4" t="n">
-        <v>108.9322353931184</v>
+        <v>73.05852605941448</v>
       </c>
       <c r="G4" t="n">
-        <v>12.44294186855885</v>
+        <v>12.44294186855884</v>
       </c>
       <c r="H4" t="n">
         <v>0.9983794689178467</v>
       </c>
       <c r="I4" t="n">
-        <v>87.57802273364777</v>
+        <v>51.70431339994391</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3642873561128681</v>
+        <v>-0.3642873561128657</v>
       </c>
       <c r="K4" t="n">
         <v>0.9988745748996735</v>
       </c>
       <c r="L4" t="n">
-        <v>84.72353346804356</v>
+        <v>48.84982413433968</v>
       </c>
       <c r="M4" t="n">
-        <v>2.868019266331444</v>
+        <v>2.86801926633145</v>
       </c>
       <c r="N4" t="n">
         <v>0.9989274144172668</v>
       </c>
       <c r="O4" t="n">
-        <v>86.62058241823887</v>
+        <v>50.746873084535</v>
       </c>
       <c r="P4" t="n">
         <v>12.38731221949801</v>
@@ -1213,7 +1213,7 @@
         <v>0.9734703898429871</v>
       </c>
       <c r="R4" t="n">
-        <v>96.17368414046916</v>
+        <v>60.2999748067653</v>
       </c>
       <c r="S4" t="n">
         <v>14.66036045804937</v>
@@ -1222,7 +1222,7 @@
         <v>0.9896765947341919</v>
       </c>
       <c r="U4" t="n">
-        <v>93.89448368802985</v>
+        <v>58.02077435432597</v>
       </c>
       <c r="V4" t="n">
         <v>23.77507635887633</v>
@@ -1231,34 +1231,34 @@
         <v>0.9514109790325165</v>
       </c>
       <c r="X4" t="n">
-        <v>54.09189792389566</v>
+        <v>18.21818859019179</v>
       </c>
       <c r="Y4" t="n">
-        <v>28.56802433095079</v>
+        <v>28.5680243309508</v>
       </c>
       <c r="Z4" t="n">
         <v>0.9921815097332001</v>
       </c>
       <c r="AA4" t="n">
-        <v>50.62212030938331</v>
+        <v>14.74841097567944</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.48580640427609</v>
+        <v>19.4858064042761</v>
       </c>
       <c r="AC4" t="n">
         <v>0.9664916694164276</v>
       </c>
       <c r="AD4" t="n">
-        <v>60.40515290929916</v>
+        <v>24.53144357559529</v>
       </c>
       <c r="AE4" t="n">
-        <v>16.44679942029587</v>
+        <v>16.44679942029588</v>
       </c>
       <c r="AF4" t="n">
         <v>0.9969249963760376</v>
       </c>
       <c r="AG4" t="n">
-        <v>60.87139616621302</v>
+        <v>24.99768683250915</v>
       </c>
       <c r="AH4" t="n">
         <v>3.774448151284076</v>
@@ -1267,16 +1267,16 @@
         <v>0.9960864782333374</v>
       </c>
       <c r="AJ4" t="n">
-        <v>71.75523068042511</v>
+        <v>35.88152134672125</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.9307130854180485</v>
+        <v>0.9307130854180519</v>
       </c>
       <c r="AL4" t="n">
         <v>0.9974183738231659</v>
       </c>
       <c r="AM4" t="n">
-        <v>35.80594164259891</v>
+        <v>-0.06776769110496517</v>
       </c>
       <c r="AN4" t="n">
         <v>22.23406040922124</v>
@@ -1285,7 +1285,7 @@
         <v>0.998983234167099</v>
       </c>
       <c r="AP4" t="n">
-        <v>26.42657198804491</v>
+        <v>-9.447137345658968</v>
       </c>
       <c r="AQ4" t="n">
         <v>29.10723584763547</v>
@@ -1294,70 +1294,70 @@
         <v>0.6204258054494858</v>
       </c>
       <c r="AS4" t="n">
-        <v>19.15734727331932</v>
+        <v>-16.71636206038455</v>
       </c>
       <c r="AT4" t="n">
-        <v>14.26377803721326</v>
+        <v>14.26377803721327</v>
       </c>
       <c r="AU4" t="n">
         <v>0.9588472843170166</v>
       </c>
       <c r="AV4" t="n">
+        <v>3.612758758220268</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-2.837575750148043</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.053386728814308</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-2.020972840329434</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.066822254911383</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.5186141805445894</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.183639688694731</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.653194366617404</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.098211775434779</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.6704908736208663</v>
+      </c>
+      <c r="BF4" t="n">
         <v>106.8629382019656</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BG4" t="n">
         <v>109.5105786099887</v>
       </c>
-      <c r="AX4" t="n">
-        <v>86.41055657977745</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.612758758220268</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-2.837575750148043</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.053386728814308</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-2.020972840329434</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.066822254911383</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-0.5186141805445894</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.183639688694731</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>-0.653194366617404</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.098211775434779</v>
-      </c>
       <c r="BH4" t="n">
-        <v>-0.6704908736208663</v>
+        <v>86.41055657977748</v>
       </c>
       <c r="BI4" t="n">
-        <v>11.09806395303272</v>
+        <v>11.09806395303279</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-3.569579528798711</v>
+        <v>-3.5695795287987</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.206523633071146</v>
+        <v>5.206523633071136</v>
       </c>
       <c r="BL4" t="n">
-        <v>-8.758428156498868</v>
+        <v>-8.758428156498884</v>
       </c>
       <c r="BM4" t="n">
         <v>-3.61589265619482</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0.466577577795297</v>
+        <v>-0.4665775777953165</v>
       </c>
     </row>
     <row r="5">
@@ -1368,16 +1368,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>127.9923824553794</v>
+        <v>92.11867312167554</v>
       </c>
       <c r="D5" t="n">
-        <v>2.864496758643625</v>
+        <v>2.864496758643617</v>
       </c>
       <c r="E5" t="n">
         <v>0.9998710453510284</v>
       </c>
       <c r="F5" t="n">
-        <v>110.853540136459</v>
+        <v>74.97983080275516</v>
       </c>
       <c r="G5" t="n">
         <v>12.37315725772939</v>
@@ -1386,25 +1386,25 @@
         <v>0.9995130300521851</v>
       </c>
       <c r="I5" t="n">
-        <v>87.72085879711395</v>
+        <v>51.84714946341008</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5283680367977013</v>
+        <v>-0.5283680367977062</v>
       </c>
       <c r="K5" t="n">
         <v>0.9983378052711487</v>
       </c>
       <c r="L5" t="n">
-        <v>84.66460451166681</v>
+        <v>48.79089517796294</v>
       </c>
       <c r="M5" t="n">
-        <v>2.936586420586764</v>
+        <v>2.936586420586769</v>
       </c>
       <c r="N5" t="n">
         <v>0.9991098940372467</v>
       </c>
       <c r="O5" t="n">
-        <v>87.9297581124813</v>
+        <v>52.05604877877743</v>
       </c>
       <c r="P5" t="n">
         <v>12.16363298132065</v>
@@ -1413,34 +1413,34 @@
         <v>0.9634585976600647</v>
       </c>
       <c r="R5" t="n">
-        <v>97.53570962459483</v>
+        <v>61.66200029089097</v>
       </c>
       <c r="S5" t="n">
-        <v>14.70110467139712</v>
+        <v>14.70110467139711</v>
       </c>
       <c r="T5" t="n">
         <v>0.9820939004421234</v>
       </c>
       <c r="U5" t="n">
-        <v>95.18836406951256</v>
+        <v>59.31465473580869</v>
       </c>
       <c r="V5" t="n">
-        <v>23.86394257241108</v>
+        <v>23.86394257241107</v>
       </c>
       <c r="W5" t="n">
         <v>0.9677639305591583</v>
       </c>
       <c r="X5" t="n">
-        <v>55.00715336901077</v>
+        <v>19.13344403530689</v>
       </c>
       <c r="Y5" t="n">
-        <v>26.93360511292802</v>
+        <v>26.93360511292803</v>
       </c>
       <c r="Z5" t="n">
         <v>0.9876953661441803</v>
       </c>
       <c r="AA5" t="n">
-        <v>52.12407619395155</v>
+        <v>16.25036686024768</v>
       </c>
       <c r="AB5" t="n">
         <v>17.62970457685755</v>
@@ -1449,7 +1449,7 @@
         <v>0.9481199383735657</v>
       </c>
       <c r="AD5" t="n">
-        <v>63.71945117382293</v>
+        <v>27.84574184011906</v>
       </c>
       <c r="AE5" t="n">
         <v>16.0366139513381</v>
@@ -1458,34 +1458,34 @@
         <v>0.9932125210762024</v>
       </c>
       <c r="AG5" t="n">
-        <v>65.02508406943464</v>
+        <v>29.15137473573077</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.750212649081618</v>
+        <v>3.750212649081616</v>
       </c>
       <c r="AI5" t="n">
         <v>0.9961986541748047</v>
       </c>
       <c r="AJ5" t="n">
-        <v>74.08988222162775</v>
+        <v>38.21617288792388</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.224336664727403</v>
+        <v>0.2243366647273936</v>
       </c>
       <c r="AL5" t="n">
         <v>0.998052179813385</v>
       </c>
       <c r="AM5" t="n">
-        <v>37.54550243945832</v>
+        <v>1.67179310575445</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.00112882573553</v>
+        <v>19.00112882573554</v>
       </c>
       <c r="AO5" t="n">
         <v>0.9990017414093018</v>
       </c>
       <c r="AP5" t="n">
-        <v>29.78896790362419</v>
+        <v>-6.08474143007968</v>
       </c>
       <c r="AQ5" t="n">
         <v>25.95116229767495</v>
@@ -1494,7 +1494,7 @@
         <v>0.2439278364181519</v>
       </c>
       <c r="AS5" t="n">
-        <v>29.0123351076816</v>
+        <v>-6.861374226022271</v>
       </c>
       <c r="AT5" t="n">
         <v>26.24377392707987</v>
@@ -1503,108 +1503,108 @@
         <v>0.7336959838867188</v>
       </c>
       <c r="AV5" t="n">
+        <v>0.2058536448377239</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.5306274332898724</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.8549122100180782</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.8599266092827991</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.8106170816624427</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.6740296140630191</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.6382627690092058</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.04009084498628823</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.1875187488312413</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.04870790116330426</v>
+      </c>
+      <c r="BF5" t="n">
         <v>117.3394523404999</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BG5" t="n">
         <v>103.8770176347002</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BH5" t="n">
         <v>80.65517605348847</v>
       </c>
-      <c r="AY5" t="n">
-        <v>0.2058536448377239</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-0.5306274332898724</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.8549122100180782</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.8599266092827991</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.8106170816624427</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-0.6740296140630191</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.6382627690092058</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-0.04009084498628823</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0.1875187488312413</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0.04870790116330426</v>
-      </c>
       <c r="BI5" t="n">
-        <v>2.415642093260445</v>
+        <v>2.415642093260406</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-2.193018544669853</v>
+        <v>-2.19301854466986</v>
       </c>
       <c r="BK5" t="n">
-        <v>-2.786055367279911</v>
+        <v>-2.786055367279943</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9629861444905696</v>
+        <v>0.9629861444905803</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.4928271952834251</v>
+        <v>-0.4928271952834642</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.197380203350944</v>
+        <v>1.197380203350942</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5.265</v>
+        <v>5.265000000000001</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>129.5892025562043</v>
+        <v>93.71549322250043</v>
       </c>
       <c r="D6" t="n">
-        <v>2.920986743683514</v>
+        <v>2.920986743683511</v>
       </c>
       <c r="E6" t="n">
         <v>0.9997636079788208</v>
       </c>
       <c r="F6" t="n">
-        <v>112.6757073909678</v>
+        <v>76.80199805726397</v>
       </c>
       <c r="G6" t="n">
-        <v>12.77803461602393</v>
+        <v>12.77803461602394</v>
       </c>
       <c r="H6" t="n">
         <v>0.9989827871322632</v>
       </c>
       <c r="I6" t="n">
-        <v>88.35312051975981</v>
+        <v>52.47941118605594</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5487969581117085</v>
+        <v>-0.5487969581117021</v>
       </c>
       <c r="K6" t="n">
         <v>0.9989380240440369</v>
       </c>
       <c r="L6" t="n">
-        <v>86.96025686061128</v>
+        <v>51.08654752690742</v>
       </c>
       <c r="M6" t="n">
-        <v>3.234051643533903</v>
+        <v>3.23405164353391</v>
       </c>
       <c r="N6" t="n">
         <v>0.9990324676036835</v>
       </c>
       <c r="O6" t="n">
-        <v>90.31841196912401</v>
+        <v>54.44470263542014</v>
       </c>
       <c r="P6" t="n">
         <v>12.44507647575216</v>
@@ -1613,7 +1613,7 @@
         <v>0.9897011816501617</v>
       </c>
       <c r="R6" t="n">
-        <v>99.37753880277594</v>
+        <v>63.50382946907207</v>
       </c>
       <c r="S6" t="n">
         <v>15.10476457311752</v>
@@ -1622,16 +1622,16 @@
         <v>0.9911164343357086</v>
       </c>
       <c r="U6" t="n">
-        <v>97.19617721882273</v>
+        <v>61.32246788511885</v>
       </c>
       <c r="V6" t="n">
-        <v>24.12933187281831</v>
+        <v>24.12933187281832</v>
       </c>
       <c r="W6" t="n">
         <v>0.9415518343448639</v>
       </c>
       <c r="X6" t="n">
-        <v>56.11724041877909</v>
+        <v>20.24353108507522</v>
       </c>
       <c r="Y6" t="n">
         <v>26.28065474489902</v>
@@ -1640,7 +1640,7 @@
         <v>0.9874438345432281</v>
       </c>
       <c r="AA6" t="n">
-        <v>53.46566869857464</v>
+        <v>17.59195936487077</v>
       </c>
       <c r="AB6" t="n">
         <v>17.03034258903341</v>
@@ -1649,34 +1649,34 @@
         <v>0.9473058879375458</v>
       </c>
       <c r="AD6" t="n">
-        <v>64.33763098209462</v>
+        <v>28.46392164839076</v>
       </c>
       <c r="AE6" t="n">
-        <v>15.95015830182014</v>
+        <v>15.95015830182015</v>
       </c>
       <c r="AF6" t="n">
         <v>0.9957652390003204</v>
       </c>
       <c r="AG6" t="n">
-        <v>65.73906553552507</v>
+        <v>29.86535620182119</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.480992418654409</v>
+        <v>3.480992418654422</v>
       </c>
       <c r="AI6" t="n">
         <v>0.9941680729389191</v>
       </c>
       <c r="AJ6" t="n">
-        <v>74.30202402967089</v>
+        <v>38.42831469596701</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.08923956688414592</v>
+        <v>-0.08923956688414228</v>
       </c>
       <c r="AL6" t="n">
         <v>0.9981892108917236</v>
       </c>
       <c r="AM6" t="n">
-        <v>39.14430902359334</v>
+        <v>3.270599689889465</v>
       </c>
       <c r="AN6" t="n">
         <v>17.97925259204621</v>
@@ -1685,7 +1685,7 @@
         <v>0.9992621839046478</v>
       </c>
       <c r="AP6" t="n">
-        <v>30.90141884824063</v>
+        <v>-4.97229048546324</v>
       </c>
       <c r="AQ6" t="n">
         <v>24.13656356486868</v>
@@ -1694,70 +1694,70 @@
         <v>0.2370745986700058</v>
       </c>
       <c r="AS6" t="n">
-        <v>30.40571618587413</v>
+        <v>-5.467993147829741</v>
       </c>
       <c r="AT6" t="n">
-        <v>25.04220110304811</v>
+        <v>25.04220110304812</v>
       </c>
       <c r="AU6" t="n">
         <v>0.9233882129192352</v>
       </c>
       <c r="AV6" t="n">
-        <v>119.0438923003547</v>
+        <v>0.16667386318775</v>
       </c>
       <c r="AW6" t="n">
-        <v>102.095401237374</v>
+        <v>-0.03371644527354078</v>
       </c>
       <c r="AX6" t="n">
-        <v>79.68931634060328</v>
+        <v>0.2862981025208811</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.16667386318775</v>
+        <v>-0.06429844714225474</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.03371644527354078</v>
+        <v>0.5014815229050669</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2862981025208811</v>
+        <v>0.1508301876960916</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.06429844714225474</v>
+        <v>0.9233251531073385</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.5014815229050669</v>
+        <v>0.1506988038407995</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1508301876960916</v>
+        <v>0.8973659353053307</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.9233251531073385</v>
+        <v>0.2025720920968572</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1506988038407995</v>
+        <v>119.0438923003548</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.8973659353053307</v>
+        <v>102.0954012373739</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.2025720920968572</v>
+        <v>79.68931634060323</v>
       </c>
       <c r="BI6" t="n">
-        <v>-1.124941057302713</v>
+        <v>-1.124941057302657</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-1.636459463028746</v>
+        <v>-1.636459463028759</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.3555863504008201</v>
+        <v>0.3555863504008343</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9209595817383374</v>
+        <v>0.9209595817383267</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.40233464485005</v>
+        <v>1.402334644850068</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.511714030716766</v>
+        <v>1.511714030716773</v>
       </c>
     </row>
     <row r="7">
@@ -1768,43 +1768,43 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>131.948876888194</v>
+        <v>96.07516755449012</v>
       </c>
       <c r="D7" t="n">
-        <v>3.725384651346403</v>
+        <v>3.72538465134641</v>
       </c>
       <c r="E7" t="n">
         <v>0.9995775520801544</v>
       </c>
       <c r="F7" t="n">
-        <v>115.005720422623</v>
+        <v>79.13201108891914</v>
       </c>
       <c r="G7" t="n">
-        <v>12.45635824000583</v>
+        <v>12.45635824000582</v>
       </c>
       <c r="H7" t="n">
         <v>0.9994206130504608</v>
       </c>
       <c r="I7" t="n">
-        <v>92.33684133976064</v>
+        <v>56.46313200605677</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.732635498046861</v>
+        <v>-1.732635498046875</v>
       </c>
       <c r="K7" t="n">
         <v>0.9993892312049866</v>
       </c>
       <c r="L7" t="n">
-        <v>94.46642449561587</v>
+        <v>58.592715161912</v>
       </c>
       <c r="M7" t="n">
-        <v>2.812649341339764</v>
+        <v>2.812649341339761</v>
       </c>
       <c r="N7" t="n">
         <v>0.9961747527122498</v>
       </c>
       <c r="O7" t="n">
-        <v>91.81960085605053</v>
+        <v>55.94589152234666</v>
       </c>
       <c r="P7" t="n">
         <v>12.66477868912068</v>
@@ -1813,7 +1813,7 @@
         <v>0.9859271049499512</v>
       </c>
       <c r="R7" t="n">
-        <v>100.3160882503428</v>
+        <v>64.44237891663897</v>
       </c>
       <c r="S7" t="n">
         <v>15.50492631628158</v>
@@ -1822,34 +1822,34 @@
         <v>0.9813496172428131</v>
       </c>
       <c r="U7" t="n">
-        <v>98.38712570515085</v>
+        <v>62.51341637144698</v>
       </c>
       <c r="V7" t="n">
-        <v>23.9569237891664</v>
+        <v>23.95692378916639</v>
       </c>
       <c r="W7" t="n">
         <v>0.9737578928470612</v>
       </c>
       <c r="X7" t="n">
-        <v>58.03761583693485</v>
+        <v>22.16390650323097</v>
       </c>
       <c r="Y7" t="n">
-        <v>26.21237166384432</v>
+        <v>26.21237166384433</v>
       </c>
       <c r="Z7" t="n">
         <v>0.9871192276477814</v>
       </c>
       <c r="AA7" t="n">
-        <v>55.41005641856093</v>
+        <v>19.53634708485705</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.17628316676364</v>
+        <v>17.17628316676363</v>
       </c>
       <c r="AC7" t="n">
         <v>0.9549660086631775</v>
       </c>
       <c r="AD7" t="n">
-        <v>65.55913154115069</v>
+        <v>29.68542220744682</v>
       </c>
       <c r="AE7" t="n">
         <v>15.2079886578499</v>
@@ -1858,7 +1858,7 @@
         <v>0.9948609173297882</v>
       </c>
       <c r="AG7" t="n">
-        <v>66.19585321304646</v>
+        <v>30.3221438793426</v>
       </c>
       <c r="AH7" t="n">
         <v>3.114132170981549</v>
@@ -1867,34 +1867,34 @@
         <v>0.9930854141712189</v>
       </c>
       <c r="AJ7" t="n">
-        <v>74.37930005661985</v>
+        <v>38.50559072291598</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.05896548007396518</v>
+        <v>-0.05896548007396942</v>
       </c>
       <c r="AL7" t="n">
         <v>0.9964973330497742</v>
       </c>
       <c r="AM7" t="n">
-        <v>40.45628283886199</v>
+        <v>4.582573505158123</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.22181052349984</v>
+        <v>18.22181052349983</v>
       </c>
       <c r="AO7" t="n">
         <v>0.9986992478370667</v>
       </c>
       <c r="AP7" t="n">
-        <v>31.22228967382553</v>
+        <v>-4.651419659878341</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23.71260866205742</v>
+        <v>23.71260866205743</v>
       </c>
       <c r="AR7" t="n">
         <v>0.1088494025170803</v>
       </c>
       <c r="AS7" t="n">
-        <v>30.65714328847033</v>
+        <v>-5.21656604523354</v>
       </c>
       <c r="AT7" t="n">
         <v>24.31193006799576</v>
@@ -1903,61 +1903,61 @@
         <v>0.9864972233772278</v>
       </c>
       <c r="AV7" t="n">
+        <v>-0.08540863686419797</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.04531170459503997</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.2180363269562413</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.02295311461103999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.7582938417475269</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.179924356176496</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.7543229042215529</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.06660299098238021</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.958126149279007</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.06931436822769399</v>
+      </c>
+      <c r="BF7" t="n">
         <v>114.2024944080946</v>
       </c>
-      <c r="AW7" t="n">
-        <v>103.9976231670011</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>84.77031275058513</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-0.08540863686419797</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-0.04531170459503997</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.2180363269562413</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-0.02295311461103999</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.7582938417475269</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.179924356176496</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.7543229042215529</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>-0.06660299098238021</v>
-      </c>
       <c r="BG7" t="n">
-        <v>0.958126149279007</v>
+        <v>103.997623167001</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.06931436822769399</v>
+        <v>84.77031275058509</v>
       </c>
       <c r="BI7" t="n">
-        <v>-2.959599860815576</v>
+        <v>-2.959599860815636</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.4674401040456555</v>
+        <v>-0.4674401040456662</v>
       </c>
       <c r="BK7" t="n">
-        <v>-1.590174119024848</v>
+        <v>-1.590174119024876</v>
       </c>
       <c r="BL7" t="n">
-        <v>-2.100809201937809</v>
+        <v>-2.100809201937778</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.2550481218906526</v>
+        <v>-0.2550481218906704</v>
       </c>
       <c r="BN7" t="n">
-        <v>-1.703895983115322</v>
+        <v>-1.703895983115302</v>
       </c>
     </row>
     <row r="8">
@@ -1968,16 +1968,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>134.912815499813</v>
+        <v>99.03910616610914</v>
       </c>
       <c r="D8" t="n">
-        <v>5.139143923495666</v>
+        <v>5.139143923495679</v>
       </c>
       <c r="E8" t="n">
         <v>0.9993746280670166</v>
       </c>
       <c r="F8" t="n">
-        <v>117.7038071003366</v>
+        <v>81.83009776663275</v>
       </c>
       <c r="G8" t="n">
         <v>13.77250184404089</v>
@@ -1986,34 +1986,34 @@
         <v>0.9991849064826965</v>
       </c>
       <c r="I8" t="n">
-        <v>104.7643742662795</v>
+        <v>68.89066493257565</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6817432160073196</v>
+        <v>-0.6817432160073139</v>
       </c>
       <c r="K8" t="n">
         <v>0.9993720352649689</v>
       </c>
       <c r="L8" t="n">
-        <v>103.1160192286715</v>
+        <v>67.2423098949676</v>
       </c>
       <c r="M8" t="n">
-        <v>4.020317564619347</v>
+        <v>4.020317564619349</v>
       </c>
       <c r="N8" t="n">
         <v>0.9964833855628967</v>
       </c>
       <c r="O8" t="n">
-        <v>94.75046928892745</v>
+        <v>58.87675995522358</v>
       </c>
       <c r="P8" t="n">
-        <v>11.65409493953622</v>
+        <v>11.65409493953624</v>
       </c>
       <c r="Q8" t="n">
         <v>0.9905543923377991</v>
       </c>
       <c r="R8" t="n">
-        <v>103.1857632576151</v>
+        <v>67.31205392391124</v>
       </c>
       <c r="S8" t="n">
         <v>15.72871106736203</v>
@@ -2022,16 +2022,16 @@
         <v>0.988434374332428</v>
       </c>
       <c r="U8" t="n">
-        <v>100.5601477115712</v>
+        <v>64.68643837786736</v>
       </c>
       <c r="V8" t="n">
-        <v>24.36443897003822</v>
+        <v>24.36443897003823</v>
       </c>
       <c r="W8" t="n">
         <v>0.9881196022033691</v>
       </c>
       <c r="X8" t="n">
-        <v>60.23524872800137</v>
+        <v>24.3615393942975</v>
       </c>
       <c r="Y8" t="n">
         <v>26.65796482816656</v>
@@ -2040,7 +2040,7 @@
         <v>0.9903469979763031</v>
       </c>
       <c r="AA8" t="n">
-        <v>57.08803217461769</v>
+        <v>21.21432284091382</v>
       </c>
       <c r="AB8" t="n">
         <v>17.46258837111453</v>
@@ -2049,34 +2049,34 @@
         <v>0.9766525626182556</v>
       </c>
       <c r="AD8" t="n">
-        <v>67.50032952491273</v>
+        <v>31.62662019120886</v>
       </c>
       <c r="AE8" t="n">
-        <v>15.27190512799203</v>
+        <v>15.27190512799202</v>
       </c>
       <c r="AF8" t="n">
         <v>0.9956469535827637</v>
       </c>
       <c r="AG8" t="n">
-        <v>66.56082843212371</v>
+        <v>30.68711909841984</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.11387244691241</v>
+        <v>3.113872446912401</v>
       </c>
       <c r="AI8" t="n">
         <v>0.9942754507064819</v>
       </c>
       <c r="AJ8" t="n">
-        <v>74.27532926518867</v>
+        <v>38.4016199314848</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.00875757095661811</v>
+        <v>0.008757570956615692</v>
       </c>
       <c r="AL8" t="n">
         <v>0.996921718120575</v>
       </c>
       <c r="AM8" t="n">
-        <v>42.1521876720672</v>
+        <v>6.278478338363325</v>
       </c>
       <c r="AN8" t="n">
         <v>18.91729476604056</v>
@@ -2085,16 +2085,16 @@
         <v>0.9994302988052368</v>
       </c>
       <c r="AP8" t="n">
-        <v>30.2810882000213</v>
+        <v>-5.592621133682572</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23.82444828114612</v>
+        <v>23.82444828114611</v>
       </c>
       <c r="AR8" t="n">
         <v>0.1280673779547215</v>
       </c>
       <c r="AS8" t="n">
-        <v>30.10047750270113</v>
+        <v>-5.77323183100274</v>
       </c>
       <c r="AT8" t="n">
         <v>24.21510574665476</v>
@@ -2103,61 +2103,61 @@
         <v>0.9729456305503845</v>
       </c>
       <c r="AV8" t="n">
+        <v>0.05235469087641675</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.1027502912156137</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.009782263573175243</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.1255258600762534</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.867433750883059</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0.07131860611286456</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.187747590085294</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.2391115148016754</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.441179437840239</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.2002061681544536</v>
+      </c>
+      <c r="BF8" t="n">
         <v>107.4913360996518</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BG8" t="n">
         <v>97.49660828887696</v>
       </c>
-      <c r="AX8" t="n">
-        <v>83.03572522810572</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.05235469087641675</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.1027502912156137</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.009782263573175243</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-0.1255258600762534</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.867433750883059</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-0.07131860611286456</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.187747590085294</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0.2391115148016754</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.441179437840239</v>
-      </c>
       <c r="BH8" t="n">
-        <v>0.2002061681544536</v>
+        <v>83.03572522810575</v>
       </c>
       <c r="BI8" t="n">
-        <v>-3.644336033245789</v>
+        <v>-3.644336033245775</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0.318902126047595</v>
+        <v>-0.3189021260475737</v>
       </c>
       <c r="BK8" t="n">
-        <v>-1.354191633172697</v>
+        <v>-1.35419163317264</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.329124778705749</v>
+        <v>1.329124778705738</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.307855867144088</v>
+        <v>1.307855867144131</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.87311140017068</v>
+        <v>1.873111400170666</v>
       </c>
     </row>
     <row r="9">
@@ -2168,61 +2168,61 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>137.5986545643908</v>
+        <v>101.7249452306869</v>
       </c>
       <c r="D9" t="n">
-        <v>4.493583516871695</v>
+        <v>4.493583516871675</v>
       </c>
       <c r="E9" t="n">
         <v>0.9995075762271881</v>
       </c>
       <c r="F9" t="n">
-        <v>120.5943168477809</v>
+        <v>84.72060751407705</v>
       </c>
       <c r="G9" t="n">
-        <v>12.82168449239529</v>
+        <v>12.82168449239528</v>
       </c>
       <c r="H9" t="n">
         <v>0.9996411502361298</v>
       </c>
       <c r="I9" t="n">
-        <v>113.6893252108959</v>
+        <v>77.81561587719207</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.05230193442486097</v>
+        <v>-0.05230193442486705</v>
       </c>
       <c r="K9" t="n">
         <v>0.9993718564510345</v>
       </c>
       <c r="L9" t="n">
-        <v>109.2301389004322</v>
+        <v>73.35642956672831</v>
       </c>
       <c r="M9" t="n">
-        <v>3.165103019552035</v>
+        <v>3.165103019552028</v>
       </c>
       <c r="N9" t="n">
         <v>0.9986360371112823</v>
       </c>
       <c r="O9" t="n">
-        <v>98.6948419124522</v>
+        <v>62.82113257874834</v>
       </c>
       <c r="P9" t="n">
-        <v>9.510527265832792</v>
+        <v>9.51052726583278</v>
       </c>
       <c r="Q9" t="n">
         <v>0.9847606420516968</v>
       </c>
       <c r="R9" t="n">
-        <v>106.9533206046896</v>
+        <v>71.07961127098571</v>
       </c>
       <c r="S9" t="n">
-        <v>14.49790305279672</v>
+        <v>14.49790305279671</v>
       </c>
       <c r="T9" t="n">
         <v>0.990912526845932</v>
       </c>
       <c r="U9" t="n">
-        <v>104.3084246047</v>
+        <v>68.43471527099609</v>
       </c>
       <c r="V9" t="n">
         <v>22.89724147066157</v>
@@ -2231,7 +2231,7 @@
         <v>0.9886335730552673</v>
       </c>
       <c r="X9" t="n">
-        <v>63.23370629168572</v>
+        <v>27.35999695798185</v>
       </c>
       <c r="Y9" t="n">
         <v>27.17877245963888</v>
@@ -2240,7 +2240,7 @@
         <v>0.9923734962940216</v>
       </c>
       <c r="AA9" t="n">
-        <v>59.72245398988115</v>
+        <v>23.84874465617728</v>
       </c>
       <c r="AB9" t="n">
         <v>18.0484690564744</v>
@@ -2249,34 +2249,34 @@
         <v>0.9768189787864685</v>
       </c>
       <c r="AD9" t="n">
-        <v>69.15625308422332</v>
+        <v>33.28254375051945</v>
       </c>
       <c r="AE9" t="n">
-        <v>14.64629477642953</v>
+        <v>14.64629477642952</v>
       </c>
       <c r="AF9" t="n">
         <v>0.9969436228275299</v>
       </c>
       <c r="AG9" t="n">
-        <v>66.42370021089594</v>
+        <v>30.54999087719207</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.26844073356466</v>
+        <v>3.268440733564661</v>
       </c>
       <c r="AI9" t="n">
         <v>0.9948570430278778</v>
       </c>
       <c r="AJ9" t="n">
-        <v>74.58235963861993</v>
+        <v>38.70865030491606</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.1999388349817224</v>
+        <v>-0.1999388349817154</v>
       </c>
       <c r="AL9" t="n">
         <v>0.9979599714279175</v>
       </c>
       <c r="AM9" t="n">
-        <v>43.91879223762675</v>
+        <v>8.045082903922879</v>
       </c>
       <c r="AN9" t="n">
         <v>20.83176146162317</v>
@@ -2285,7 +2285,7 @@
         <v>0.9994907975196838</v>
       </c>
       <c r="AP9" t="n">
-        <v>29.04587400720474</v>
+        <v>-6.827835326499125</v>
       </c>
       <c r="AQ9" t="n">
         <v>24.53274422503532</v>
@@ -2294,7 +2294,7 @@
         <v>0.6071343570947647</v>
       </c>
       <c r="AS9" t="n">
-        <v>30.25681515957447</v>
+        <v>-5.616894174129401</v>
       </c>
       <c r="AT9" t="n">
         <v>24.48976800796834</v>
@@ -2303,126 +2303,126 @@
         <v>0.3390203602612019</v>
       </c>
       <c r="AV9" t="n">
-        <v>99.50456928701871</v>
+        <v>0.2350847771827169</v>
       </c>
       <c r="AW9" t="n">
-        <v>96.31209252557585</v>
+        <v>0.0496570100175564</v>
       </c>
       <c r="AX9" t="n">
-        <v>88.79358330630902</v>
+        <v>0.01088203267848442</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.2350847771827169</v>
+        <v>0.1231604434074249</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0496570100175564</v>
+        <v>1.098508023201152</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01088203267848442</v>
+        <v>0.1878078947675998</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.1231604434074249</v>
+        <v>1.342874892214512</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.098508023201152</v>
+        <v>0.0333922974606784</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.1878078947675998</v>
+        <v>1.298148581322202</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.342874892214512</v>
+        <v>-0.1382508176438364</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0333922974606784</v>
+        <v>99.50456928701868</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.298148581322202</v>
+        <v>96.31209252557586</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.1382508176438364</v>
+        <v>88.79358330630905</v>
       </c>
       <c r="BI9" t="n">
-        <v>-4.982173262588891</v>
+        <v>-4.982173262588915</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0.3022182141802983</v>
+        <v>-0.3022182141802805</v>
       </c>
       <c r="BK9" t="n">
-        <v>-1.978547634200314</v>
+        <v>-1.978547634200364</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0.8308319907317649</v>
+        <v>-0.8308319907317898</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.946646467124321</v>
+        <v>3.946646467124282</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.6031263837257583</v>
+        <v>0.6031263837257317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5.345</v>
+        <v>5.345000000000001</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>140.0110123005319</v>
+        <v>104.137302966828</v>
       </c>
       <c r="D10" t="n">
-        <v>5.360826532891451</v>
+        <v>5.360826532891457</v>
       </c>
       <c r="E10" t="n">
         <v>0.9992612302303314</v>
       </c>
       <c r="F10" t="n">
-        <v>123.5729136365525</v>
+        <v>87.69920430284867</v>
       </c>
       <c r="G10" t="n">
-        <v>13.47996326203041</v>
+        <v>13.47996326203042</v>
       </c>
       <c r="H10" t="n">
         <v>0.9996453821659088</v>
       </c>
       <c r="I10" t="n">
-        <v>120.5762173267121</v>
+        <v>84.70250799300823</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8781189614153959</v>
+        <v>0.8781189614153924</v>
       </c>
       <c r="K10" t="n">
         <v>0.9976740479469299</v>
       </c>
       <c r="L10" t="n">
-        <v>115.6132271949281</v>
+        <v>79.73951786122424</v>
       </c>
       <c r="M10" t="n">
-        <v>2.981340124251986</v>
+        <v>2.981340124251995</v>
       </c>
       <c r="N10" t="n">
         <v>0.9979694783687592</v>
       </c>
       <c r="O10" t="n">
-        <v>104.05788015812</v>
+        <v>68.18417082441616</v>
       </c>
       <c r="P10" t="n">
-        <v>9.481365122693646</v>
+        <v>9.481365122693651</v>
       </c>
       <c r="Q10" t="n">
         <v>0.9798175394535065</v>
       </c>
       <c r="R10" t="n">
-        <v>111.2557390902905</v>
+        <v>75.3820297565866</v>
       </c>
       <c r="S10" t="n">
-        <v>14.61199496654753</v>
+        <v>14.61199496654754</v>
       </c>
       <c r="T10" t="n">
         <v>0.9919470250606537</v>
       </c>
       <c r="U10" t="n">
-        <v>108.5010609728225</v>
+        <v>72.62735163911861</v>
       </c>
       <c r="V10" t="n">
         <v>23.08473789945562</v>
@@ -2431,16 +2431,16 @@
         <v>0.9885475933551788</v>
       </c>
       <c r="X10" t="n">
-        <v>65.67916058479472</v>
+        <v>29.80545125109084</v>
       </c>
       <c r="Y10" t="n">
-        <v>27.24860576873131</v>
+        <v>27.2486057687313</v>
       </c>
       <c r="Z10" t="n">
         <v>0.9891091585159302</v>
       </c>
       <c r="AA10" t="n">
-        <v>62.49044499498733</v>
+        <v>26.61673566128346</v>
       </c>
       <c r="AB10" t="n">
         <v>18.17924824166806</v>
@@ -2449,7 +2449,7 @@
         <v>0.9894557893276215</v>
       </c>
       <c r="AD10" t="n">
-        <v>71.56340822260431</v>
+        <v>35.68969888890044</v>
       </c>
       <c r="AE10" t="n">
         <v>13.68980407714844</v>
@@ -2458,7 +2458,7 @@
         <v>0.9957732260227203</v>
       </c>
       <c r="AG10" t="n">
-        <v>66.77921376329788</v>
+        <v>30.905504429594</v>
       </c>
       <c r="AH10" t="n">
         <v>3.208541870117188</v>
@@ -2467,97 +2467,97 @@
         <v>0.9964268803596497</v>
       </c>
       <c r="AJ10" t="n">
-        <v>75.08801805212143</v>
+        <v>39.21430871841756</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.6373141674285137</v>
+        <v>-0.637314167428524</v>
       </c>
       <c r="AL10" t="n">
         <v>0.9981057345867157</v>
       </c>
       <c r="AM10" t="n">
-        <v>46.46174451138111</v>
+        <v>10.58803517767724</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.81894829932681</v>
+        <v>21.8189482993268</v>
       </c>
       <c r="AO10" t="n">
         <v>0.9997505843639374</v>
       </c>
       <c r="AP10" t="n">
-        <v>28.90858142933947</v>
+        <v>-6.965127904364401</v>
       </c>
       <c r="AQ10" t="n">
-        <v>24.61874129924369</v>
+        <v>24.61874129924368</v>
       </c>
       <c r="AR10" t="n">
         <v>0.9151338636875153</v>
       </c>
       <c r="AS10" t="n">
-        <v>23.58204050266997</v>
+        <v>-12.29166883103391</v>
       </c>
       <c r="AT10" t="n">
-        <v>11.5290459166182</v>
+        <v>11.52904591661819</v>
       </c>
       <c r="AU10" t="n">
         <v>0.1055279104039073</v>
       </c>
       <c r="AV10" t="n">
-        <v>90.30892961766439</v>
+        <v>0.2051353454589844</v>
       </c>
       <c r="AW10" t="n">
-        <v>91.80424879934766</v>
+        <v>-0.0787400184793654</v>
       </c>
       <c r="AX10" t="n">
-        <v>96.96394691941535</v>
+        <v>0.2523635296111415</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.2051353454589844</v>
+        <v>-0.05967160488696877</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.0787400184793654</v>
+        <v>1.0154257429407</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.2523635296111415</v>
+        <v>-0.1152758902691779</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0.05967160488696877</v>
+        <v>1.225535413052175</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.0154257429407</v>
+        <v>-0.1178929146299978</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.1152758902691779</v>
+        <v>1.218908391100296</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.225535413052175</v>
+        <v>0.001070854511667996</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.1178929146299978</v>
+        <v>90.30892961766445</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.218908391100296</v>
+        <v>91.80424879934762</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.001070854511667996</v>
+        <v>96.96394691941529</v>
       </c>
       <c r="BI10" t="n">
-        <v>-3.230646622938242</v>
+        <v>-3.230646622938206</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.06006459336962067</v>
+        <v>0.06006459336958692</v>
       </c>
       <c r="BK10" t="n">
-        <v>-1.400174284350371</v>
+        <v>-1.400174284350353</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.2856095982184179</v>
+        <v>0.2856095982184339</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.85013298129536</v>
+        <v>2.850132981295356</v>
       </c>
       <c r="BN10" t="n">
-        <v>-0.6410753565352927</v>
+        <v>-0.6410753565352678</v>
       </c>
     </row>
     <row r="11">
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>142.331362785177</v>
+        <v>106.4576534514732</v>
       </c>
       <c r="D11" t="n">
         <v>4.363721482297208</v>
@@ -2577,7 +2577,7 @@
         <v>0.9995887279510498</v>
       </c>
       <c r="F11" t="n">
-        <v>126.3832457522129</v>
+        <v>90.50953641850899</v>
       </c>
       <c r="G11" t="n">
         <v>13.21088912639212</v>
@@ -2586,34 +2586,34 @@
         <v>0.9995560944080353</v>
       </c>
       <c r="I11" t="n">
-        <v>125.0748776374979</v>
+        <v>89.20116830379406</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7624118886095346</v>
+        <v>0.7624118886095412</v>
       </c>
       <c r="K11" t="n">
         <v>0.9978981912136078</v>
       </c>
       <c r="L11" t="n">
-        <v>119.8154084225918</v>
+        <v>83.94169908888797</v>
       </c>
       <c r="M11" t="n">
-        <v>2.56455604066241</v>
+        <v>2.5645560406624</v>
       </c>
       <c r="N11" t="n">
         <v>0.9977489411830902</v>
       </c>
       <c r="O11" t="n">
-        <v>108.1442731492063</v>
+        <v>72.27056381550241</v>
       </c>
       <c r="P11" t="n">
-        <v>8.522967074779757</v>
+        <v>8.522967074779753</v>
       </c>
       <c r="Q11" t="n">
         <v>0.9846097528934479</v>
       </c>
       <c r="R11" t="n">
-        <v>115.3915608182867</v>
+        <v>79.51785148458279</v>
       </c>
       <c r="S11" t="n">
         <v>14.07465021660988</v>
@@ -2622,16 +2622,16 @@
         <v>0.9929244220256805</v>
       </c>
       <c r="U11" t="n">
-        <v>112.0665327031562</v>
+        <v>76.1928233694523</v>
       </c>
       <c r="V11" t="n">
-        <v>22.58525604897358</v>
+        <v>22.58525604897357</v>
       </c>
       <c r="W11" t="n">
         <v>0.9881849586963654</v>
       </c>
       <c r="X11" t="n">
-        <v>68.12889829595039</v>
+        <v>32.25518896224651</v>
       </c>
       <c r="Y11" t="n">
         <v>28.42302525297124</v>
@@ -2640,52 +2640,52 @@
         <v>0.9840058088302612</v>
       </c>
       <c r="AA11" t="n">
-        <v>64.78686434157352</v>
+        <v>28.91315500786965</v>
       </c>
       <c r="AB11" t="n">
-        <v>19.39095842077379</v>
+        <v>19.39095842077377</v>
       </c>
       <c r="AC11" t="n">
         <v>0.9894709885120392</v>
       </c>
       <c r="AD11" t="n">
-        <v>73.50945979990858</v>
+        <v>37.63575046620471</v>
       </c>
       <c r="AE11" t="n">
-        <v>13.75314428451213</v>
+        <v>13.75314428451214</v>
       </c>
       <c r="AF11" t="n">
         <v>0.9951954483985901</v>
       </c>
       <c r="AG11" t="n">
-        <v>66.89604089615193</v>
+        <v>31.02233156244806</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.122307960023278</v>
+        <v>4.122307960023272</v>
       </c>
       <c r="AI11" t="n">
         <v>0.9968036115169525</v>
       </c>
       <c r="AJ11" t="n">
-        <v>75.27871639170546</v>
+        <v>39.40500705800159</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.07054755028258342</v>
+        <v>0.07054755028257979</v>
       </c>
       <c r="AL11" t="n">
         <v>0.9980523884296417</v>
       </c>
       <c r="AM11" t="n">
-        <v>49.3132712993216</v>
+        <v>13.43956196561773</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.49076778330702</v>
+        <v>23.49076778330701</v>
       </c>
       <c r="AO11" t="n">
         <v>0.99978107213974</v>
       </c>
       <c r="AP11" t="n">
-        <v>30.29623538889783</v>
+        <v>-5.577473944806036</v>
       </c>
       <c r="AQ11" t="n">
         <v>23.88299982598488</v>
@@ -2694,70 +2694,70 @@
         <v>0.9075405597686768</v>
       </c>
       <c r="AS11" t="n">
-        <v>22.5751613048797</v>
+        <v>-13.29854802882417</v>
       </c>
       <c r="AT11" t="n">
-        <v>13.0482775099734</v>
+        <v>13.04827750997341</v>
       </c>
       <c r="AU11" t="n">
         <v>0.1952073276042938</v>
       </c>
       <c r="AV11" t="n">
-        <v>81.35354832178854</v>
+        <v>0.02486046324385427</v>
       </c>
       <c r="AW11" t="n">
-        <v>88.43884346599316</v>
+        <v>0.005846835197285571</v>
       </c>
       <c r="AX11" t="n">
+        <v>-0.04682845257698176</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.08223107520570139</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.004143978687043</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0.05711190243984987</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.352120460347924</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.06023417127893094</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.341536704530107</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.02462813194761715</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>81.35354832178855</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>88.4388434659931</v>
+      </c>
+      <c r="BH11" t="n">
         <v>102.5700091063805</v>
       </c>
-      <c r="AY11" t="n">
-        <v>0.02486046324385427</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.005846835197285571</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-0.04682845257698176</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.08223107520570139</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.004143978687043</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-0.05711190243984987</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.352120460347924</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0.06023417127893094</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1.341536704530107</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0.02462813194761715</v>
-      </c>
       <c r="BI11" t="n">
-        <v>-5.297138890803318</v>
+        <v>-5.297138890803311</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6637527491058464</v>
+        <v>0.6637527491058623</v>
       </c>
       <c r="BK11" t="n">
-        <v>-1.992898694141523</v>
+        <v>-1.99289869414153</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.3164392460259293</v>
+        <v>0.3164392460259435</v>
       </c>
       <c r="BM11" t="n">
-        <v>3.747448845298646</v>
+        <v>3.747448845298663</v>
       </c>
       <c r="BN11" t="n">
-        <v>-0.1990023119639961</v>
+        <v>-0.1990023119639783</v>
       </c>
     </row>
     <row r="12">
@@ -2768,196 +2768,196 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>144.6030880542512</v>
+        <v>108.7293787205473</v>
       </c>
       <c r="D12" t="n">
-        <v>5.073644759807166</v>
+        <v>5.073644759807181</v>
       </c>
       <c r="E12" t="n">
         <v>0.9994515478610992</v>
       </c>
       <c r="F12" t="n">
-        <v>128.5033286886012</v>
+        <v>92.62961935489736</v>
       </c>
       <c r="G12" t="n">
-        <v>13.67822200693982</v>
+        <v>13.67822200693983</v>
       </c>
       <c r="H12" t="n">
         <v>0.9998848438262939</v>
       </c>
       <c r="I12" t="n">
-        <v>129.7845962199759</v>
+        <v>93.91088688627204</v>
       </c>
       <c r="J12" t="n">
-        <v>1.569106731008958</v>
+        <v>1.569106731008976</v>
       </c>
       <c r="K12" t="n">
         <v>0.9977866411209106</v>
       </c>
       <c r="L12" t="n">
-        <v>124.2149231281686</v>
+        <v>88.34121379446476</v>
       </c>
       <c r="M12" t="n">
-        <v>3.034291368849722</v>
+        <v>3.034291368849734</v>
       </c>
       <c r="N12" t="n">
         <v>0.9972403645515442</v>
       </c>
       <c r="O12" t="n">
-        <v>111.8632986190471</v>
+        <v>75.98958928534326</v>
       </c>
       <c r="P12" t="n">
-        <v>8.651911958735027</v>
+        <v>8.651911958735042</v>
       </c>
       <c r="Q12" t="n">
         <v>0.9827552437782288</v>
       </c>
       <c r="R12" t="n">
-        <v>118.7116704088576</v>
+        <v>82.83796107515377</v>
       </c>
       <c r="S12" t="n">
-        <v>14.23371497620927</v>
+        <v>14.23371497620928</v>
       </c>
       <c r="T12" t="n">
         <v>0.9938614070415497</v>
       </c>
       <c r="U12" t="n">
-        <v>115.2764787065222</v>
+        <v>79.40276937281833</v>
       </c>
       <c r="V12" t="n">
-        <v>22.4107782891456</v>
+        <v>22.41077828914561</v>
       </c>
       <c r="W12" t="n">
         <v>0.987411230802536</v>
       </c>
       <c r="X12" t="n">
-        <v>70.67714853489653</v>
+        <v>34.80343920119265</v>
       </c>
       <c r="Y12" t="n">
-        <v>28.29658021318153</v>
+        <v>28.29658021318152</v>
       </c>
       <c r="Z12" t="n">
         <v>0.9885424077510834</v>
       </c>
       <c r="AA12" t="n">
-        <v>67.32422037327544</v>
+        <v>31.45051103957156</v>
       </c>
       <c r="AB12" t="n">
-        <v>19.34086414093669</v>
+        <v>19.34086414093667</v>
       </c>
       <c r="AC12" t="n">
         <v>0.9904165863990784</v>
       </c>
       <c r="AD12" t="n">
-        <v>75.22706376745346</v>
+        <v>39.35335443374959</v>
       </c>
       <c r="AE12" t="n">
-        <v>13.18747337828293</v>
+        <v>13.18747337828291</v>
       </c>
       <c r="AF12" t="n">
         <v>0.9882522225379944</v>
       </c>
       <c r="AG12" t="n">
-        <v>67.34179232982879</v>
+        <v>31.46808299612492</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.296404250124681</v>
+        <v>4.296404250124668</v>
       </c>
       <c r="AI12" t="n">
         <v>0.9914266765117645</v>
       </c>
       <c r="AJ12" t="n">
-        <v>75.49280207207863</v>
+        <v>39.61909273837476</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.2104251942736255</v>
+        <v>0.2104251942736037</v>
       </c>
       <c r="AL12" t="n">
         <v>0.9978437721729279</v>
       </c>
       <c r="AM12" t="n">
-        <v>51.8976536202938</v>
+        <v>16.02394428658993</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.23433084690826</v>
+        <v>23.23433084690824</v>
       </c>
       <c r="AO12" t="n">
         <v>0.9998842477798462</v>
       </c>
       <c r="AP12" t="n">
-        <v>32.54783914444295</v>
+        <v>-3.325870189260925</v>
       </c>
       <c r="AQ12" t="n">
-        <v>22.05715585262219</v>
+        <v>22.05715585262217</v>
       </c>
       <c r="AR12" t="n">
         <v>0.8451331853866577</v>
       </c>
       <c r="AS12" t="n">
-        <v>21.76284790039062</v>
+        <v>-14.11086143331324</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.903246291140306</v>
+        <v>9.903246291140293</v>
       </c>
       <c r="AU12" t="n">
         <v>0.5740960836410522</v>
       </c>
       <c r="AV12" t="n">
-        <v>75.05317802233608</v>
+        <v>0.1934010931786041</v>
       </c>
       <c r="AW12" t="n">
+        <v>0.04319333015603988</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.2819974371727483</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.07766307668482852</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.6503612437146771</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.209227014095223</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.8536044587480269</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.2838261584018102</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.9820735200922535</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0.2300627688144097</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>75.05317802233611</v>
+      </c>
+      <c r="BG12" t="n">
         <v>86.33919511674236</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BH12" t="n">
         <v>107.3800620454897</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0.1934010931786041</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.04319333015603988</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.2819974371727483</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-0.07766307668482852</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.6503612437146771</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-0.209227014095223</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0.8536044587480269</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>-0.2838261584018102</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0.9820735200922535</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>-0.2300627688144097</v>
       </c>
       <c r="BI12" t="n">
         <v>-1.666091030711371</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.841605580940529</v>
+        <v>0.8416055809405307</v>
       </c>
       <c r="BK12" t="n">
-        <v>-1.158786654929344</v>
+        <v>-1.158786654929315</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0.2230081901549514</v>
+        <v>-0.2230081901549656</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.02974610471622441</v>
+        <v>0.02974610471623862</v>
       </c>
       <c r="BN12" t="n">
-        <v>-1.349357730808052</v>
+        <v>-1.349357730808082</v>
       </c>
     </row>
     <row r="13">
@@ -2968,16 +2968,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>147.1279550105967</v>
+        <v>111.2542456768929</v>
       </c>
       <c r="D13" t="n">
-        <v>5.753521209067486</v>
+        <v>5.753521209067487</v>
       </c>
       <c r="E13" t="n">
         <v>0.9996575117111206</v>
       </c>
       <c r="F13" t="n">
-        <v>130.7699284654983</v>
+        <v>94.89621913179438</v>
       </c>
       <c r="G13" t="n">
         <v>14.15897125893451</v>
@@ -2986,7 +2986,7 @@
         <v>0.9997817873954773</v>
       </c>
       <c r="I13" t="n">
-        <v>134.1823699626517</v>
+        <v>98.30866062894782</v>
       </c>
       <c r="J13" t="n">
         <v>2.098749039020944</v>
@@ -2995,34 +2995,34 @@
         <v>0.9978145658969879</v>
       </c>
       <c r="L13" t="n">
-        <v>129.0799282966776</v>
+        <v>93.20621896297375</v>
       </c>
       <c r="M13" t="n">
-        <v>3.067292558385972</v>
+        <v>3.067292558385971</v>
       </c>
       <c r="N13" t="n">
         <v>0.9938232004642487</v>
       </c>
       <c r="O13" t="n">
-        <v>115.2925126096036</v>
+        <v>79.41880327589969</v>
       </c>
       <c r="P13" t="n">
-        <v>8.344958690886799</v>
+        <v>8.344958690886802</v>
       </c>
       <c r="Q13" t="n">
         <v>0.9792607724666595</v>
       </c>
       <c r="R13" t="n">
-        <v>121.6580573548662</v>
+        <v>85.78434802116233</v>
       </c>
       <c r="S13" t="n">
-        <v>14.24795921812667</v>
+        <v>14.24795921812666</v>
       </c>
       <c r="T13" t="n">
         <v>0.9946523606777191</v>
       </c>
       <c r="U13" t="n">
-        <v>118.2961808874252</v>
+        <v>82.42247155372134</v>
       </c>
       <c r="V13" t="n">
         <v>22.62076519905253</v>
@@ -3031,7 +3031,7 @@
         <v>0.9859694242477417</v>
       </c>
       <c r="X13" t="n">
-        <v>72.30514769858502</v>
+        <v>36.43143836488115</v>
       </c>
       <c r="Y13" t="n">
         <v>27.61497091739736</v>
@@ -3040,7 +3040,7 @@
         <v>0.9922653436660767</v>
       </c>
       <c r="AA13" t="n">
-        <v>68.72627177137011</v>
+        <v>32.85256243766623</v>
       </c>
       <c r="AB13" t="n">
         <v>19.12205472905585</v>
@@ -3049,7 +3049,7 @@
         <v>0.9940783083438873</v>
       </c>
       <c r="AD13" t="n">
-        <v>76.10775967861744</v>
+        <v>40.23405034491357</v>
       </c>
       <c r="AE13" t="n">
         <v>13.00461140084774</v>
@@ -3058,25 +3058,25 @@
         <v>0.984354704618454</v>
       </c>
       <c r="AG13" t="n">
-        <v>67.47689145676634</v>
+        <v>31.60318212306247</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.754322133165715</v>
+        <v>4.754322133165725</v>
       </c>
       <c r="AI13" t="n">
         <v>0.9959903955459595</v>
       </c>
       <c r="AJ13" t="n">
-        <v>75.87966107307597</v>
+        <v>40.00595173937209</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.2087288714469793</v>
+        <v>0.2087288714469747</v>
       </c>
       <c r="AL13" t="n">
         <v>0.9975077211856842</v>
       </c>
       <c r="AM13" t="n">
-        <v>54.28372038171646</v>
+        <v>18.4100110480126</v>
       </c>
       <c r="AN13" t="n">
         <v>22.32661145798703</v>
@@ -3085,79 +3085,79 @@
         <v>0.9983724355697632</v>
       </c>
       <c r="AP13" t="n">
-        <v>32.49831402555425</v>
+        <v>-3.375395308149617</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20.38960558302858</v>
+        <v>20.38960558302859</v>
       </c>
       <c r="AR13" t="n">
         <v>0.8995852768421173</v>
       </c>
       <c r="AS13" t="n">
-        <v>22.90418401677558</v>
+        <v>-12.96952531692829</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.601736515126319</v>
+        <v>8.60173651512633</v>
       </c>
       <c r="AU13" t="n">
         <v>0.2056230567395687</v>
       </c>
       <c r="AV13" t="n">
-        <v>72.11923004664574</v>
+        <v>0.08079650554251216</v>
       </c>
       <c r="AW13" t="n">
-        <v>83.34751400687176</v>
+        <v>-0.1143516378199774</v>
       </c>
       <c r="AX13" t="n">
-        <v>106.7926840613667</v>
+        <v>0.1584195076151111</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.08079650554251216</v>
+        <v>0.08990155889632589</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.1143516378199774</v>
+        <v>0.5461956592316319</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.1584195076151111</v>
+        <v>0.0950366892713177</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.08990155889632589</v>
+        <v>0.8942391010040929</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.5461956592316319</v>
+        <v>0.04049564929718485</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0950366892713177</v>
+        <v>0.9089551073439566</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.8942391010040929</v>
+        <v>0.07919250650608767</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.04049564929718485</v>
+        <v>72.11923004664578</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.9089551073439566</v>
+        <v>83.34751400687175</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.07919250650608767</v>
+        <v>106.7926840613666</v>
       </c>
       <c r="BI13" t="n">
-        <v>-1.31988702904701</v>
+        <v>-1.319887029047031</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.1459394790806456</v>
+        <v>0.1459394790806368</v>
       </c>
       <c r="BK13" t="n">
-        <v>-1.871215376406944</v>
+        <v>-1.871215376406973</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0.332303580211228</v>
+        <v>-0.3323035802112262</v>
       </c>
       <c r="BM13" t="n">
         <v>0.5296632537628909</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.3059879277968669</v>
+        <v>0.3059879277968793</v>
       </c>
     </row>
     <row r="14">
@@ -3168,43 +3168,43 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>148.8695185235206</v>
+        <v>112.9958091898168</v>
       </c>
       <c r="D14" t="n">
-        <v>6.647718713638639</v>
+        <v>6.64771871363863</v>
       </c>
       <c r="E14" t="n">
         <v>0.9996997117996216</v>
       </c>
       <c r="F14" t="n">
-        <v>133.1430435180664</v>
+        <v>97.26933418436255</v>
       </c>
       <c r="G14" t="n">
-        <v>14.91856676466921</v>
+        <v>14.91856676466922</v>
       </c>
       <c r="H14" t="n">
         <v>0.9999339580535889</v>
       </c>
       <c r="I14" t="n">
-        <v>135.6268984206179</v>
+        <v>99.75318908691408</v>
       </c>
       <c r="J14" t="n">
-        <v>1.851499841568327</v>
+        <v>1.851499841568318</v>
       </c>
       <c r="K14" t="n">
         <v>0.997392863035202</v>
       </c>
       <c r="L14" t="n">
-        <v>130.6330214155481</v>
+        <v>94.75931208184426</v>
       </c>
       <c r="M14" t="n">
-        <v>3.418699223944486</v>
+        <v>3.418699223944482</v>
       </c>
       <c r="N14" t="n">
         <v>0.9977990090847015</v>
       </c>
       <c r="O14" t="n">
-        <v>117.2448827865276</v>
+        <v>81.37117345282373</v>
       </c>
       <c r="P14" t="n">
         <v>8.818248992270611</v>
@@ -3213,7 +3213,7 @@
         <v>0.9824889004230499</v>
       </c>
       <c r="R14" t="n">
-        <v>123.7199986234624</v>
+        <v>87.84628928975857</v>
       </c>
       <c r="S14" t="n">
         <v>14.66783564141456</v>
@@ -3222,7 +3222,7 @@
         <v>0.9959750175476074</v>
       </c>
       <c r="U14" t="n">
-        <v>119.9918341129384</v>
+        <v>84.11812477923455</v>
       </c>
       <c r="V14" t="n">
         <v>23.03934300199468</v>
@@ -3231,16 +3231,16 @@
         <v>0.9901803731918335</v>
       </c>
       <c r="X14" t="n">
-        <v>74.24991688829788</v>
+        <v>38.376207554594</v>
       </c>
       <c r="Y14" t="n">
-        <v>27.04842344243475</v>
+        <v>27.04842344243476</v>
       </c>
       <c r="Z14" t="n">
         <v>0.9871596097946167</v>
       </c>
       <c r="AA14" t="n">
-        <v>70.29030576665352</v>
+        <v>34.41659643294964</v>
       </c>
       <c r="AB14" t="n">
         <v>18.6189610907372</v>
@@ -3249,34 +3249,34 @@
         <v>0.9934022724628448</v>
       </c>
       <c r="AD14" t="n">
-        <v>77.36860234686669</v>
+        <v>41.49489301316282</v>
       </c>
       <c r="AE14" t="n">
-        <v>12.11285692580202</v>
+        <v>12.11285692580203</v>
       </c>
       <c r="AF14" t="n">
         <v>0.9890359938144684</v>
       </c>
       <c r="AG14" t="n">
-        <v>67.97159681928919</v>
+        <v>32.09788748558532</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.171341591692979</v>
+        <v>5.171341591692986</v>
       </c>
       <c r="AI14" t="n">
         <v>0.9962406158447266</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75.80911352279338</v>
+        <v>39.93540418908952</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.01899232255651384</v>
+        <v>0.01899232255651596</v>
       </c>
       <c r="AL14" t="n">
         <v>0.9977743327617645</v>
       </c>
       <c r="AM14" t="n">
-        <v>56.64401155837039</v>
+        <v>20.77030222466652</v>
       </c>
       <c r="AN14" t="n">
         <v>21.4556836067362</v>
@@ -3285,7 +3285,7 @@
         <v>0.9986467957496643</v>
       </c>
       <c r="AP14" t="n">
-        <v>33.19215470171989</v>
+        <v>-2.681554631983978</v>
       </c>
       <c r="AQ14" t="n">
         <v>21.30334732380319</v>
@@ -3294,70 +3294,70 @@
         <v>0.9017288386821747</v>
       </c>
       <c r="AS14" t="n">
-        <v>21.51644584980417</v>
+        <v>-14.3572634838997</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.75838778881315</v>
+        <v>10.75838778881316</v>
       </c>
       <c r="AU14" t="n">
         <v>0.4356501251459122</v>
       </c>
       <c r="AV14" t="n">
-        <v>69.76903998727798</v>
+        <v>-0.02492539426113893</v>
       </c>
       <c r="AW14" t="n">
-        <v>79.02661857615625</v>
+        <v>-0.04910509637061722</v>
       </c>
       <c r="AX14" t="n">
+        <v>0.194080839765828</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.09216501357707507</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.4752909883539722</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.05578284567975089</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.5966267687209097</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.03762448087651649</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.8709745204195087</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-0.04360320720266841</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>69.76903998727801</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>79.02661857615624</v>
+      </c>
+      <c r="BH14" t="n">
         <v>107.4292577884311</v>
       </c>
-      <c r="AY14" t="n">
-        <v>-0.02492539426113893</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-0.04910509637061722</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0.194080839765828</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-0.09216501357707507</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0.4752909883539722</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>-0.05578284567975089</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.5966267687209097</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0.03762448087651649</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0.8709745204195087</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>-0.04360320720266841</v>
-      </c>
       <c r="BI14" t="n">
-        <v>-1.298568030909877</v>
+        <v>-1.298568030909848</v>
       </c>
       <c r="BJ14" t="n">
-        <v>-0.5709824577502154</v>
+        <v>-0.5709824577502136</v>
       </c>
       <c r="BK14" t="n">
-        <v>-1.006566675424416</v>
+        <v>-1.006566675424395</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.8925909029008352</v>
+        <v>0.8925909029008388</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.4891287384745802</v>
+        <v>0.4891287384745588</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.002694184539036</v>
+        <v>1.002694184539033</v>
       </c>
     </row>
     <row r="15">
@@ -3368,16 +3368,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>150.4161347734167</v>
+        <v>114.5424254397129</v>
       </c>
       <c r="D15" t="n">
-        <v>6.776549968313688</v>
+        <v>6.776549968313664</v>
       </c>
       <c r="E15" t="n">
         <v>0.9999440908432007</v>
       </c>
       <c r="F15" t="n">
-        <v>134.5265287034055</v>
+        <v>98.65281936970163</v>
       </c>
       <c r="G15" t="n">
         <v>15.24223165309176</v>
@@ -3386,97 +3386,97 @@
         <v>0.9999045133590698</v>
       </c>
       <c r="I15" t="n">
-        <v>135.7891163927443</v>
+        <v>99.91540705904049</v>
       </c>
       <c r="J15" t="n">
-        <v>1.79388168010307</v>
+        <v>1.793881680103059</v>
       </c>
       <c r="K15" t="n">
         <v>0.9982866644859314</v>
       </c>
       <c r="L15" t="n">
-        <v>130.8245800911112</v>
+        <v>94.95087075740734</v>
       </c>
       <c r="M15" t="n">
-        <v>3.545533849837938</v>
+        <v>3.545533849837932</v>
       </c>
       <c r="N15" t="n">
         <v>0.9985491335391998</v>
       </c>
       <c r="O15" t="n">
-        <v>118.6858968531832</v>
+        <v>82.81218751947931</v>
       </c>
       <c r="P15" t="n">
-        <v>9.251655416285757</v>
+        <v>9.25165541628574</v>
       </c>
       <c r="Q15" t="n">
         <v>0.9831584393978119</v>
       </c>
       <c r="R15" t="n">
-        <v>125.3656346747216</v>
+        <v>89.49192534101772</v>
       </c>
       <c r="S15" t="n">
-        <v>15.28238337090676</v>
+        <v>15.28238337090675</v>
       </c>
       <c r="T15" t="n">
         <v>0.9972067773342133</v>
       </c>
       <c r="U15" t="n">
-        <v>121.5823356141435</v>
+        <v>85.70862628043966</v>
       </c>
       <c r="V15" t="n">
-        <v>23.34248157257731</v>
+        <v>23.3424815725773</v>
       </c>
       <c r="W15" t="n">
         <v>0.9896387755870819</v>
       </c>
       <c r="X15" t="n">
-        <v>76.02027324920005</v>
+        <v>40.14656391549618</v>
       </c>
       <c r="Y15" t="n">
-        <v>26.35814179765418</v>
+        <v>26.35814179765417</v>
       </c>
       <c r="Z15" t="n">
         <v>0.9916987419128418</v>
       </c>
       <c r="AA15" t="n">
-        <v>72.00483768544299</v>
+        <v>36.13112835173911</v>
       </c>
       <c r="AB15" t="n">
-        <v>18.0431771785655</v>
+        <v>18.04317717856549</v>
       </c>
       <c r="AC15" t="n">
         <v>0.9925952553749084</v>
       </c>
       <c r="AD15" t="n">
-        <v>78.40631363239694</v>
+        <v>42.53260429869307</v>
       </c>
       <c r="AE15" t="n">
-        <v>10.96454376870014</v>
+        <v>10.96454376870013</v>
       </c>
       <c r="AF15" t="n">
         <v>0.9880499243736267</v>
       </c>
       <c r="AG15" t="n">
-        <v>68.09764212750375</v>
+        <v>32.22393279379987</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.926340630713938</v>
+        <v>4.926340630713931</v>
       </c>
       <c r="AI15" t="n">
         <v>0.9968619644641876</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75.54214558702834</v>
+        <v>39.66843625332447</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.232972490026583</v>
+        <v>-0.2329724900265958</v>
       </c>
       <c r="AL15" t="n">
         <v>0.9975487887859344</v>
       </c>
       <c r="AM15" t="n">
-        <v>59.30821236143721</v>
+        <v>23.43450302773334</v>
       </c>
       <c r="AN15" t="n">
         <v>20.04995954797623</v>
@@ -3485,79 +3485,79 @@
         <v>0.9994328618049622</v>
       </c>
       <c r="AP15" t="n">
-        <v>30.54049167227238</v>
+        <v>-5.333217661431492</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21.27138503054356</v>
+        <v>21.27138503054355</v>
       </c>
       <c r="AR15" t="n">
         <v>0.9180121719837189</v>
       </c>
       <c r="AS15" t="n">
-        <v>15.58463269091667</v>
+        <v>-20.2890766427872</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.0315447868185</v>
+        <v>8.031544786818484</v>
       </c>
       <c r="AU15" t="n">
         <v>0.4436362981796265</v>
       </c>
       <c r="AV15" t="n">
-        <v>65.13492009690935</v>
+        <v>-0.2854996539176753</v>
       </c>
       <c r="AW15" t="n">
+        <v>-0.02207147314193314</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.135773800789039</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.01597100115836803</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.4738340986535903</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.03949834945353992</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.9040649901045121</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.02292673638526388</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.7430157762892691</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-0.1895255230842761</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>65.13492009690938</v>
+      </c>
+      <c r="BG15" t="n">
         <v>78.27608675704408</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BH15" t="n">
         <v>112.0766082536517</v>
       </c>
-      <c r="AY15" t="n">
-        <v>-0.2854996539176753</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-0.02207147314193314</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>-0.135773800789039</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-0.01597100115836803</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.4738340986535903</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-0.03949834945353992</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0.9040649901045121</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>-0.02292673638526388</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0.7430157762892691</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>-0.1895255230842761</v>
-      </c>
       <c r="BI15" t="n">
-        <v>-2.398649608598431</v>
+        <v>-2.398649608598463</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.9608753746542193</v>
+        <v>0.960875374654214</v>
       </c>
       <c r="BK15" t="n">
         <v>-1.154909164217912</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0.5530125519152858</v>
+        <v>-0.5530125519153017</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.083712263802155</v>
+        <v>3.083712263802191</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.3777745624384004</v>
+        <v>0.3777745624384146</v>
       </c>
     </row>
     <row r="16">
@@ -3568,16 +3568,16 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>151.9965638505652</v>
+        <v>116.1228545168613</v>
       </c>
       <c r="D16" t="n">
-        <v>7.113793555726403</v>
+        <v>7.113793555726397</v>
       </c>
       <c r="E16" t="n">
         <v>0.9996461272239685</v>
       </c>
       <c r="F16" t="n">
-        <v>135.7185566678961</v>
+        <v>99.84484733419217</v>
       </c>
       <c r="G16" t="n">
         <v>15.6694696304646</v>
@@ -3586,34 +3586,34 @@
         <v>0.9999219179153442</v>
       </c>
       <c r="I16" t="n">
-        <v>135.9220220687542</v>
+        <v>100.0483127350503</v>
       </c>
       <c r="J16" t="n">
-        <v>1.771959345391451</v>
+        <v>1.771959345391456</v>
       </c>
       <c r="K16" t="n">
         <v>0.9987602233886719</v>
       </c>
       <c r="L16" t="n">
-        <v>131.0748729299992</v>
+        <v>95.2011635962953</v>
       </c>
       <c r="M16" t="n">
-        <v>3.728249732484215</v>
+        <v>3.728249732484209</v>
       </c>
       <c r="N16" t="n">
         <v>0.9991569221019745</v>
       </c>
       <c r="O16" t="n">
-        <v>119.2450746576837</v>
+        <v>83.3713653239798</v>
       </c>
       <c r="P16" t="n">
-        <v>9.495511968085111</v>
+        <v>9.495511968085108</v>
       </c>
       <c r="Q16" t="n">
         <v>0.9817647933959961</v>
       </c>
       <c r="R16" t="n">
-        <v>126.151697686378</v>
+        <v>90.27798835267413</v>
       </c>
       <c r="S16" t="n">
         <v>15.58556252337517</v>
@@ -3622,7 +3622,7 @@
         <v>0.9953378438949585</v>
       </c>
       <c r="U16" t="n">
-        <v>122.7615437609084</v>
+        <v>86.88783442720455</v>
       </c>
       <c r="V16" t="n">
         <v>23.87029769572806</v>
@@ -3631,16 +3631,16 @@
         <v>0.9923319518566132</v>
       </c>
       <c r="X16" t="n">
-        <v>77.03252751776512</v>
+        <v>41.15881818406125</v>
       </c>
       <c r="Y16" t="n">
-        <v>25.875955946902</v>
+        <v>25.87595594690201</v>
       </c>
       <c r="Z16" t="n">
         <v>0.9912880063056946</v>
       </c>
       <c r="AA16" t="n">
-        <v>73.62766265869141</v>
+        <v>37.75395332498753</v>
       </c>
       <c r="AB16" t="n">
         <v>17.44352300116356</v>
@@ -3649,34 +3649,34 @@
         <v>0.9937968552112579</v>
       </c>
       <c r="AD16" t="n">
-        <v>79.28603152011303</v>
+        <v>43.41232218640916</v>
       </c>
       <c r="AE16" t="n">
-        <v>10.65114609738613</v>
+        <v>10.65114609738614</v>
       </c>
       <c r="AF16" t="n">
         <v>0.9703747630119324</v>
       </c>
       <c r="AG16" t="n">
-        <v>68.15980343108481</v>
+        <v>32.28609409738095</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.439035943213909</v>
+        <v>5.439035943213931</v>
       </c>
       <c r="AI16" t="n">
         <v>0.9988738000392914</v>
       </c>
       <c r="AJ16" t="n">
-        <v>75.18689175869557</v>
+        <v>39.31318242499169</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.2940482281624099</v>
+        <v>-0.2940482281624003</v>
       </c>
       <c r="AL16" t="n">
         <v>0.9974673092365265</v>
       </c>
       <c r="AM16" t="n">
-        <v>61.88058447330556</v>
+        <v>26.00687513960169</v>
       </c>
       <c r="AN16" t="n">
         <v>18.69533619982131</v>
@@ -3685,7 +3685,7 @@
         <v>0.9997602105140686</v>
       </c>
       <c r="AP16" t="n">
-        <v>34.84540290020882</v>
+        <v>-1.028306433495054</v>
       </c>
       <c r="AQ16" t="n">
         <v>20.12139178336935</v>
@@ -3694,70 +3694,70 @@
         <v>0.9671794176101685</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.006427957656536</v>
+        <v>-26.86728137604734</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.251577174409903</v>
+        <v>7.251577174409907</v>
       </c>
       <c r="AU16" t="n">
         <v>0.9856441915035248</v>
       </c>
       <c r="AV16" t="n">
+        <v>-0.01517153800802262</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.08608939799856508</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.2499590528772231</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.0443184629399731</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.6612087817902292</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.09376951988707205</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.8813147849224983</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.03088991692725784</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.5560732902364549</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.09381923269718584</v>
+      </c>
+      <c r="BF16" t="n">
         <v>64.3443017051576</v>
       </c>
-      <c r="AW16" t="n">
-        <v>75.31350473027078</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
+        <v>75.31350473027072</v>
+      </c>
+      <c r="BH16" t="n">
         <v>118.2350569686259</v>
       </c>
-      <c r="AY16" t="n">
-        <v>-0.01517153800802262</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.08608939799856508</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0.2499590528772231</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0.0443184629399731</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0.6612087817902292</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0.09376951988707205</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0.8813147849224983</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0.03088991692725784</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0.5560732902364549</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0.09381923269718584</v>
-      </c>
       <c r="BI16" t="n">
-        <v>0.2351840370678122</v>
+        <v>0.2351840370678246</v>
       </c>
       <c r="BJ16" t="n">
-        <v>-0.5232020576778158</v>
+        <v>-0.5232020576777883</v>
       </c>
       <c r="BK16" t="n">
-        <v>-1.793066299249951</v>
+        <v>-1.793066299249965</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0.457966869507743</v>
+        <v>-0.4579668695077075</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.90128231847654</v>
+        <v>2.901282318476511</v>
       </c>
       <c r="BN16" t="n">
-        <v>-0.05838157200336802</v>
+        <v>-0.05838157200340355</v>
       </c>
     </row>
     <row r="17">
@@ -3768,52 +3768,52 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>153.4150874361079</v>
+        <v>117.541378102404</v>
       </c>
       <c r="D17" t="n">
-        <v>6.619627932284743</v>
+        <v>6.619627932284741</v>
       </c>
       <c r="E17" t="n">
         <v>0.999816507101059</v>
       </c>
       <c r="F17" t="n">
-        <v>137.3038677459068</v>
+        <v>101.4301584122029</v>
       </c>
       <c r="G17" t="n">
-        <v>15.84635795430935</v>
+        <v>15.84635795430934</v>
       </c>
       <c r="H17" t="n">
         <v>0.9999411106109619</v>
       </c>
       <c r="I17" t="n">
-        <v>136.1680335186898</v>
+        <v>100.2943241849859</v>
       </c>
       <c r="J17" t="n">
-        <v>1.615418779089097</v>
+        <v>1.615418779089096</v>
       </c>
       <c r="K17" t="n">
         <v>0.999021053314209</v>
       </c>
       <c r="L17" t="n">
-        <v>131.5891915179313</v>
+        <v>95.71548218422748</v>
       </c>
       <c r="M17" t="n">
-        <v>3.656038324883653</v>
+        <v>3.656038324883644</v>
       </c>
       <c r="N17" t="n">
         <v>0.9990971684455872</v>
       </c>
       <c r="O17" t="n">
-        <v>120.6231624522108</v>
+        <v>84.74945311850692</v>
       </c>
       <c r="P17" t="n">
-        <v>9.814582987034598</v>
+        <v>9.814582987034576</v>
       </c>
       <c r="Q17" t="n">
         <v>0.9889732897281647</v>
       </c>
       <c r="R17" t="n">
-        <v>127.4614618179646</v>
+        <v>91.58775248426073</v>
       </c>
       <c r="S17" t="n">
         <v>15.84298154141041</v>
@@ -3822,25 +3822,25 @@
         <v>0.9943977892398834</v>
       </c>
       <c r="U17" t="n">
-        <v>123.8539066720516</v>
+        <v>87.98019733834775</v>
       </c>
       <c r="V17" t="n">
-        <v>24.10055931578293</v>
+        <v>24.10055931578291</v>
       </c>
       <c r="W17" t="n">
         <v>0.9896790683269501</v>
       </c>
       <c r="X17" t="n">
-        <v>78.42005871711893</v>
+        <v>42.54634938341507</v>
       </c>
       <c r="Y17" t="n">
-        <v>25.55812673365817</v>
+        <v>25.55812673365816</v>
       </c>
       <c r="Z17" t="n">
         <v>0.991519421339035</v>
       </c>
       <c r="AA17" t="n">
-        <v>75.37404729964885</v>
+        <v>39.50033796594499</v>
       </c>
       <c r="AB17" t="n">
         <v>17.22580930019947</v>
@@ -3849,7 +3849,7 @@
         <v>0.9887924492359161</v>
       </c>
       <c r="AD17" t="n">
-        <v>80.54082748737741</v>
+        <v>44.66711815367354</v>
       </c>
       <c r="AE17" t="n">
         <v>10.05652407382397</v>
@@ -3858,106 +3858,106 @@
         <v>0.9749289453029633</v>
       </c>
       <c r="AG17" t="n">
-        <v>68.39923858642578</v>
+        <v>32.52552925272192</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.510649336145292</v>
+        <v>6.51064933614528</v>
       </c>
       <c r="AI17" t="n">
         <v>0.999206930398941</v>
       </c>
       <c r="AJ17" t="n">
-        <v>75.17599552235706</v>
+        <v>39.30228618865318</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.3126184991065344</v>
+        <v>-0.3126184991065492</v>
       </c>
       <c r="AL17" t="n">
         <v>0.9962741136550903</v>
       </c>
       <c r="AM17" t="n">
-        <v>63.79304033644656</v>
+        <v>27.91933100274269</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.96504081563748</v>
+        <v>17.96504081563747</v>
       </c>
       <c r="AO17" t="n">
         <v>0.9997883439064026</v>
       </c>
       <c r="AP17" t="n">
-        <v>36.88760513954975</v>
+        <v>1.013895805845873</v>
       </c>
       <c r="AQ17" t="n">
-        <v>19.23982336166058</v>
+        <v>19.23982336166057</v>
       </c>
       <c r="AR17" t="n">
         <v>0.9395397007465363</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.005727351980006</v>
+        <v>-27.86798198172387</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.084444735912584</v>
+        <v>7.084444735912567</v>
       </c>
       <c r="AU17" t="n">
         <v>0.9826448857784271</v>
       </c>
       <c r="AV17" t="n">
-        <v>61.4608750826946</v>
+        <v>-0.09521322047456593</v>
       </c>
       <c r="AW17" t="n">
-        <v>70.51905522546649</v>
+        <v>-0.06061209009048518</v>
       </c>
       <c r="AX17" t="n">
-        <v>124.1599793955866</v>
+        <v>-0.01998657875872567</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.09521322047456593</v>
+        <v>-0.02613118354310551</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0.06061209009048518</v>
+        <v>0.4410621967721475</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.01998657875872567</v>
+        <v>-0.1971224521068802</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0.02613118354310551</v>
+        <v>0.8398644467617657</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.4410621967721475</v>
+        <v>-0.1292228698730469</v>
       </c>
       <c r="BD17" t="n">
-        <v>-0.1971224521068802</v>
+        <v>0.7975314525847743</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.8398644467617657</v>
+        <v>0.01853983452979158</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.1292228698730469</v>
+        <v>61.46087508269467</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.7975314525847743</v>
+        <v>70.51905522546653</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.01853983452979158</v>
+        <v>124.1599793955865</v>
       </c>
       <c r="BI17" t="n">
-        <v>-2.747934920734659</v>
+        <v>-2.747934920734632</v>
       </c>
       <c r="BJ17" t="n">
-        <v>-0.0217803252921529</v>
+        <v>-0.02178032529218665</v>
       </c>
       <c r="BK17" t="n">
-        <v>-2.52575040320114</v>
+        <v>-2.525750403201116</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.6591425208727131</v>
+        <v>0.6591425208726793</v>
       </c>
       <c r="BM17" t="n">
-        <v>3.371380078451498</v>
+        <v>3.371380078451484</v>
       </c>
       <c r="BN17" t="n">
-        <v>-0.3758352650197381</v>
+        <v>-0.3758352650197079</v>
       </c>
     </row>
     <row r="18">
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>154.4189777780086</v>
+        <v>118.5452684443048</v>
       </c>
       <c r="D18" t="n">
-        <v>6.279056630236028</v>
+        <v>6.279056630236037</v>
       </c>
       <c r="E18" t="n">
         <v>0.9999440908432007</v>
       </c>
       <c r="F18" t="n">
-        <v>138.7351989746094</v>
+        <v>102.8614896409055</v>
       </c>
       <c r="G18" t="n">
         <v>15.85660893866356</v>
@@ -3986,25 +3986,25 @@
         <v>0.999835729598999</v>
       </c>
       <c r="I18" t="n">
-        <v>136.3199112263132</v>
+        <v>100.4462018926093</v>
       </c>
       <c r="J18" t="n">
-        <v>1.62397344061668</v>
+        <v>1.623973440616689</v>
       </c>
       <c r="K18" t="n">
         <v>0.9990429282188416</v>
       </c>
       <c r="L18" t="n">
-        <v>131.7371936554605</v>
+        <v>95.86348432175659</v>
       </c>
       <c r="M18" t="n">
-        <v>3.839208724650916</v>
+        <v>3.839208724650931</v>
       </c>
       <c r="N18" t="n">
         <v>0.9988478422164917</v>
       </c>
       <c r="O18" t="n">
-        <v>121.2662960620637</v>
+        <v>85.3925867283598</v>
       </c>
       <c r="P18" t="n">
         <v>10.20166924659242</v>
@@ -4013,7 +4013,7 @@
         <v>0.9904111623764038</v>
       </c>
       <c r="R18" t="n">
-        <v>128.3343538324884</v>
+        <v>92.4606444987845</v>
       </c>
       <c r="S18" t="n">
         <v>16.04232788085938</v>
@@ -4022,61 +4022,61 @@
         <v>0.9955398440361023</v>
       </c>
       <c r="U18" t="n">
-        <v>124.7041742852394</v>
+        <v>88.8304649515355</v>
       </c>
       <c r="V18" t="n">
-        <v>24.32606473882146</v>
+        <v>24.32606473882148</v>
       </c>
       <c r="W18" t="n">
         <v>0.992497444152832</v>
       </c>
       <c r="X18" t="n">
-        <v>79.65560263775765</v>
+        <v>43.78189330405378</v>
       </c>
       <c r="Y18" t="n">
-        <v>25.15977900078954</v>
+        <v>25.15977900078956</v>
       </c>
       <c r="Z18" t="n">
         <v>0.99299556016922</v>
       </c>
       <c r="AA18" t="n">
-        <v>76.46487621550865</v>
+        <v>40.59116688180478</v>
       </c>
       <c r="AB18" t="n">
-        <v>16.79885539602725</v>
+        <v>16.79885539602726</v>
       </c>
       <c r="AC18" t="n">
         <v>0.9926474094390869</v>
       </c>
       <c r="AD18" t="n">
-        <v>81.16524067330869</v>
+        <v>45.29153133960482</v>
       </c>
       <c r="AE18" t="n">
-        <v>9.206877363489014</v>
+        <v>9.20687736348903</v>
       </c>
       <c r="AF18" t="n">
         <v>0.952348530292511</v>
       </c>
       <c r="AG18" t="n">
-        <v>68.30575821247507</v>
+        <v>32.4320488787712</v>
       </c>
       <c r="AH18" t="n">
-        <v>7.601847547165875</v>
+        <v>7.601847547165892</v>
       </c>
       <c r="AI18" t="n">
         <v>0.9978728294372559</v>
       </c>
       <c r="AJ18" t="n">
-        <v>74.91726165122175</v>
+        <v>39.04355231751788</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0.1945170950382362</v>
+        <v>-0.1945170950382314</v>
       </c>
       <c r="AL18" t="n">
         <v>0.9950226545333862</v>
       </c>
       <c r="AM18" t="n">
-        <v>65.20164165091008</v>
+        <v>29.3279323172062</v>
       </c>
       <c r="AN18" t="n">
         <v>17.123185827377</v>
@@ -4085,7 +4085,7 @@
         <v>0.9997292160987854</v>
       </c>
       <c r="AP18" t="n">
-        <v>36.85759280590301</v>
+        <v>0.983883472199139</v>
       </c>
       <c r="AQ18" t="n">
         <v>17.5594410997756</v>
@@ -4094,67 +4094,67 @@
         <v>0.8910297751426697</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.759197275689308</v>
+        <v>-27.11451205801456</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.09206893596243</v>
+        <v>5.092068935962434</v>
       </c>
       <c r="AU18" t="n">
         <v>0.9457923769950867</v>
       </c>
       <c r="AV18" t="n">
-        <v>56.81572260860776</v>
+        <v>-0.09781857754321521</v>
       </c>
       <c r="AW18" t="n">
-        <v>65.35188135016851</v>
+        <v>-0.02561934450839587</v>
       </c>
       <c r="AX18" t="n">
+        <v>0.1726150512695312</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.133301349396401</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.06052788267744802</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.1963554544651771</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.4074624244202951</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.1830364795441355</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.6119991870636596</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0.1164436340332031</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>56.81572260860781</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>65.3518813501685</v>
+      </c>
+      <c r="BH18" t="n">
         <v>127.3493794903544</v>
       </c>
-      <c r="AY18" t="n">
-        <v>-0.09781857754321521</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-0.02561934450839587</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0.1726150512695312</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0.133301349396401</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0.06052788267744802</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>-0.1963554544651771</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0.4074624244202951</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>-0.1830364795441355</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0.6119991870636596</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>-0.1164436340332031</v>
-      </c>
       <c r="BI18" t="n">
-        <v>0.0661723169098245</v>
+        <v>0.06617231690977476</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.525719832521455</v>
+        <v>2.52571983252143</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.4610805889930489</v>
+        <v>0.4610805889930276</v>
       </c>
       <c r="BL18" t="n">
-        <v>2.88827819262514</v>
+        <v>2.888278192625165</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.240557375619638</v>
+        <v>1.240557375619652</v>
       </c>
       <c r="BN18" t="n">
         <v>-0.7859839870275955</v>
@@ -4168,25 +4168,25 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>154.9634730562251</v>
+        <v>119.0897637225212</v>
       </c>
       <c r="D19" t="n">
-        <v>6.228946117644625</v>
+        <v>6.228946117644615</v>
       </c>
       <c r="E19" t="n">
         <v>0.9999356269836426</v>
       </c>
       <c r="F19" t="n">
-        <v>139.3608580244349</v>
+        <v>103.487148690731</v>
       </c>
       <c r="G19" t="n">
-        <v>16.00830402780088</v>
+        <v>16.00830402780086</v>
       </c>
       <c r="H19" t="n">
         <v>0.9998958110809326</v>
       </c>
       <c r="I19" t="n">
-        <v>136.2904000789561</v>
+        <v>100.4166907452522</v>
       </c>
       <c r="J19" t="n">
         <v>1.46331787109375</v>
@@ -4195,16 +4195,16 @@
         <v>0.9991323351860046</v>
       </c>
       <c r="L19" t="n">
-        <v>131.8338921729555</v>
+        <v>95.9601828392516</v>
       </c>
       <c r="M19" t="n">
-        <v>3.703730157081111</v>
+        <v>3.703730157081117</v>
       </c>
       <c r="N19" t="n">
         <v>0.9992437362670898</v>
       </c>
       <c r="O19" t="n">
-        <v>121.6974542496052</v>
+        <v>85.82374491590136</v>
       </c>
       <c r="P19" t="n">
         <v>10.28421280231882</v>
@@ -4213,7 +4213,7 @@
         <v>0.9843370318412781</v>
       </c>
       <c r="R19" t="n">
-        <v>128.9850356731009</v>
+        <v>93.11132633939702</v>
       </c>
       <c r="S19" t="n">
         <v>16.13654278694315</v>
@@ -4222,61 +4222,61 @@
         <v>0.9960318207740784</v>
       </c>
       <c r="U19" t="n">
-        <v>125.4747999475357</v>
+        <v>89.60109061383187</v>
       </c>
       <c r="V19" t="n">
-        <v>24.20487099505488</v>
+        <v>24.20487099505485</v>
       </c>
       <c r="W19" t="n">
         <v>0.9900258779525757</v>
       </c>
       <c r="X19" t="n">
-        <v>80.10789587142619</v>
+        <v>44.23418653772232</v>
       </c>
       <c r="Y19" t="n">
-        <v>25.45229323366857</v>
+        <v>25.45229323366855</v>
       </c>
       <c r="Z19" t="n">
         <v>0.9939205646514893</v>
       </c>
       <c r="AA19" t="n">
-        <v>76.74220470671959</v>
+        <v>40.86849537301572</v>
       </c>
       <c r="AB19" t="n">
-        <v>17.37284558884642</v>
+        <v>17.37284558884641</v>
       </c>
       <c r="AC19" t="n">
         <v>0.99398273229599</v>
       </c>
       <c r="AD19" t="n">
-        <v>80.84902661911985</v>
+        <v>44.97531728541598</v>
       </c>
       <c r="AE19" t="n">
-        <v>9.507491740774611</v>
+        <v>9.507491740774602</v>
       </c>
       <c r="AF19" t="n">
         <v>0.9491029977798462</v>
       </c>
       <c r="AG19" t="n">
-        <v>68.7625398027136</v>
+        <v>32.88883046900973</v>
       </c>
       <c r="AH19" t="n">
-        <v>7.605857037483389</v>
+        <v>7.605857037483378</v>
       </c>
       <c r="AI19" t="n">
         <v>0.9976736903190613</v>
       </c>
       <c r="AJ19" t="n">
-        <v>74.92804020009143</v>
+        <v>39.05433086638756</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.06894050760470805</v>
+        <v>-0.06894050760472074</v>
       </c>
       <c r="AL19" t="n">
         <v>0.9942591190338135</v>
       </c>
       <c r="AM19" t="n">
-        <v>65.6854345443401</v>
+        <v>29.81172521063623</v>
       </c>
       <c r="AN19" t="n">
         <v>17.30176235767121</v>
@@ -4285,79 +4285,79 @@
         <v>0.9996868371963501</v>
       </c>
       <c r="AP19" t="n">
-        <v>35.52224585350524</v>
+        <v>-0.3514634801986318</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16.28718274704954</v>
+        <v>16.28718274704953</v>
       </c>
       <c r="AR19" t="n">
         <v>0.9501581192016602</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.66754929562832</v>
+        <v>-25.20616003807555</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.408342726687181</v>
+        <v>3.408342726687168</v>
       </c>
       <c r="AU19" t="n">
         <v>0.7986185550689697</v>
       </c>
       <c r="AV19" t="n">
+        <v>-0.2067647081740347</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.08900622104076916</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.2288980686918194</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.03789536496426393</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.01306736722905555</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.2166423391788541</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.4559577779566979</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.01977961114112148</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.6168040823429166</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-0.08678639188725512</v>
+      </c>
+      <c r="BF19" t="n">
         <v>60.16493170951819</v>
       </c>
-      <c r="AW19" t="n">
-        <v>71.3704702581376</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>129.8137420345823</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>-0.2067647081740347</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>-0.08900622104076916</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0.2288980686918194</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>-0.03789536496426393</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0.01306736722905555</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0.2166423391788541</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0.4559577779566979</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0.01977961114112148</v>
-      </c>
       <c r="BG19" t="n">
-        <v>0.6168040823429166</v>
+        <v>71.37047025813762</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.08678639188725512</v>
+        <v>129.8137420345822</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.014719424501465</v>
+        <v>2.014719424501411</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.430258073938564</v>
+        <v>0.4302580739385817</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.1575963749438</v>
+        <v>3.157596374943829</v>
       </c>
       <c r="BL19" t="n">
         <v>-1.68411704058423</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.609056017206932</v>
+        <v>1.609056017206946</v>
       </c>
       <c r="BN19" t="n">
-        <v>-1.188715117058759</v>
+        <v>-1.188715117058745</v>
       </c>
     </row>
     <row r="20">
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>155.7732764710771</v>
+        <v>119.8995671373733</v>
       </c>
       <c r="D20" t="n">
-        <v>6.271962916597431</v>
+        <v>6.271962916597407</v>
       </c>
       <c r="E20" t="n">
         <v>0.9995213747024536</v>
       </c>
       <c r="F20" t="n">
-        <v>139.7609304874501</v>
+        <v>103.8872211537463</v>
       </c>
       <c r="G20" t="n">
         <v>16.06922555477061</v>
@@ -4386,43 +4386,43 @@
         <v>0.999882698059082</v>
       </c>
       <c r="I20" t="n">
-        <v>136.2757419018035</v>
+        <v>100.4020325680997</v>
       </c>
       <c r="J20" t="n">
-        <v>1.478398099858708</v>
+        <v>1.47839809985871</v>
       </c>
       <c r="K20" t="n">
         <v>0.9991408586502075</v>
       </c>
       <c r="L20" t="n">
-        <v>131.6559406037026</v>
+        <v>95.78223126999877</v>
       </c>
       <c r="M20" t="n">
-        <v>3.901623665018292</v>
+        <v>3.901623665018285</v>
       </c>
       <c r="N20" t="n">
         <v>0.9989416003227234</v>
       </c>
       <c r="O20" t="n">
-        <v>121.6333024045254</v>
+        <v>85.75959307082157</v>
       </c>
       <c r="P20" t="n">
-        <v>10.63894718251331</v>
+        <v>10.6389471825133</v>
       </c>
       <c r="Q20" t="n">
         <v>0.9836435914039612</v>
       </c>
       <c r="R20" t="n">
-        <v>129.4627088181516</v>
+        <v>93.58899948444774</v>
       </c>
       <c r="S20" t="n">
-        <v>16.29604583090926</v>
+        <v>16.29604583090924</v>
       </c>
       <c r="T20" t="n">
         <v>0.9952175617218018</v>
       </c>
       <c r="U20" t="n">
-        <v>125.7991222625083</v>
+        <v>89.92541292880445</v>
       </c>
       <c r="V20" t="n">
         <v>24.41807199031749</v>
@@ -4431,61 +4431,61 @@
         <v>0.9923098087310791</v>
       </c>
       <c r="X20" t="n">
-        <v>80.88921080244349</v>
+        <v>45.01550146873961</v>
       </c>
       <c r="Y20" t="n">
-        <v>25.63180314733629</v>
+        <v>25.63180314733627</v>
       </c>
       <c r="Z20" t="n">
         <v>0.9927655458450317</v>
       </c>
       <c r="AA20" t="n">
-        <v>77.37679177142205</v>
+        <v>41.50308243771818</v>
       </c>
       <c r="AB20" t="n">
-        <v>17.49804882293051</v>
+        <v>17.49804882293052</v>
       </c>
       <c r="AC20" t="n">
         <v>0.9931300282478333</v>
       </c>
       <c r="AD20" t="n">
-        <v>81.1913754077668</v>
+        <v>45.31766607406293</v>
       </c>
       <c r="AE20" t="n">
-        <v>9.703339921667236</v>
+        <v>9.70333992166722</v>
       </c>
       <c r="AF20" t="n">
         <v>0.9568681716918945</v>
       </c>
       <c r="AG20" t="n">
-        <v>68.76355434985871</v>
+        <v>32.88984501615484</v>
       </c>
       <c r="AH20" t="n">
-        <v>8.013461498504</v>
+        <v>8.01346149850399</v>
       </c>
       <c r="AI20" t="n">
         <v>0.9979698061943054</v>
       </c>
       <c r="AJ20" t="n">
-        <v>74.50373223487368</v>
+        <v>38.63002290116981</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.3677530491605694</v>
+        <v>0.3677530491605718</v>
       </c>
       <c r="AL20" t="n">
         <v>0.9939133524894714</v>
       </c>
       <c r="AM20" t="n">
-        <v>66.16504750353225</v>
+        <v>30.29133816982838</v>
       </c>
       <c r="AN20" t="n">
-        <v>17.54341937125997</v>
+        <v>17.54341937125998</v>
       </c>
       <c r="AO20" t="n">
         <v>0.9993364214897156</v>
       </c>
       <c r="AP20" t="n">
-        <v>38.47224864553898</v>
+        <v>2.598539311835111</v>
       </c>
       <c r="AQ20" t="n">
         <v>15.96471908244681</v>
@@ -4494,70 +4494,70 @@
         <v>0.963595986366272</v>
       </c>
       <c r="AS20" t="n">
-        <v>14.46707400869816</v>
+        <v>-21.40663532500571</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.451359525639958</v>
+        <v>3.451359525639961</v>
       </c>
       <c r="AU20" t="n">
         <v>0.7720247507095337</v>
       </c>
       <c r="AV20" t="n">
-        <v>60.84516145761069</v>
+        <v>-0.2758310196247535</v>
       </c>
       <c r="AW20" t="n">
-        <v>71.66707410005611</v>
+        <v>0.01575185897502251</v>
       </c>
       <c r="AX20" t="n">
+        <v>0.09682432134100338</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-0.01792298986556418</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.4938125610351562</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0.1763364101978055</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.4470216467025381</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.0793883141050955</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.4384264032891494</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-0.08082085467399125</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>60.84516145761063</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>71.66707410005615</v>
+      </c>
+      <c r="BH20" t="n">
         <v>130.5674915247683</v>
       </c>
-      <c r="AY20" t="n">
-        <v>-0.2758310196247535</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0.01575185897502251</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0.09682432134100338</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>-0.01792298986556418</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0.4938125610351562</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0.1763364101978055</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0.4470216467025381</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0.0793883141050955</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0.4384264032891494</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>-0.08082085467399125</v>
-      </c>
       <c r="BI20" t="n">
-        <v>0.9266884647869524</v>
+        <v>0.9266884647869382</v>
       </c>
       <c r="BJ20" t="n">
-        <v>-0.6971081924710987</v>
+        <v>-0.697108192471072</v>
       </c>
       <c r="BK20" t="n">
-        <v>-2.907153492175411</v>
+        <v>-2.907153492175432</v>
       </c>
       <c r="BL20" t="n">
-        <v>-1.967376248089209</v>
+        <v>-1.967376248089234</v>
       </c>
       <c r="BM20" t="n">
-        <v>-1.136872858497881</v>
+        <v>-1.136872858497838</v>
       </c>
       <c r="BN20" t="n">
-        <v>0.2486212330913382</v>
+        <v>0.248621233091324</v>
       </c>
     </row>
     <row r="21">
@@ -4568,16 +4568,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>157.0841850118434</v>
+        <v>121.2104756781396</v>
       </c>
       <c r="D21" t="n">
-        <v>5.543469368143292</v>
+        <v>5.543469368143285</v>
       </c>
       <c r="E21" t="n">
         <v>0.9990569949150085</v>
       </c>
       <c r="F21" t="n">
-        <v>140.3670128355635</v>
+        <v>104.4933035018596</v>
       </c>
       <c r="G21" t="n">
         <v>15.48138882251496</v>
@@ -4586,43 +4586,43 @@
         <v>0.999955415725708</v>
       </c>
       <c r="I21" t="n">
-        <v>136.2558243122507</v>
+        <v>100.3821149785468</v>
       </c>
       <c r="J21" t="n">
-        <v>1.265343199384972</v>
+        <v>1.265343199384974</v>
       </c>
       <c r="K21" t="n">
         <v>0.9993888139724731</v>
       </c>
       <c r="L21" t="n">
-        <v>131.8131710620637</v>
+        <v>95.9394617283598</v>
       </c>
       <c r="M21" t="n">
-        <v>3.459654463098417</v>
+        <v>3.459654463098405</v>
       </c>
       <c r="N21" t="n">
         <v>0.9993249177932739</v>
       </c>
       <c r="O21" t="n">
-        <v>122.7270735071061</v>
+        <v>86.85336417340218</v>
       </c>
       <c r="P21" t="n">
-        <v>10.2292649289395</v>
+        <v>10.22926492893949</v>
       </c>
       <c r="Q21" t="n">
         <v>0.9863195419311523</v>
       </c>
       <c r="R21" t="n">
-        <v>130.1019627997216</v>
+        <v>94.2282534660177</v>
       </c>
       <c r="S21" t="n">
-        <v>16.04033125207781</v>
+        <v>16.0403312520778</v>
       </c>
       <c r="T21" t="n">
         <v>0.9942533373832703</v>
       </c>
       <c r="U21" t="n">
-        <v>126.2988070224194</v>
+        <v>90.42509768871551</v>
       </c>
       <c r="V21" t="n">
         <v>24.21146149330951</v>
@@ -4631,52 +4631,52 @@
         <v>0.9935012459754944</v>
       </c>
       <c r="X21" t="n">
-        <v>80.98474867800449</v>
+        <v>45.11103934430062</v>
       </c>
       <c r="Y21" t="n">
-        <v>24.99514640645779</v>
+        <v>24.99514640645778</v>
       </c>
       <c r="Z21" t="n">
         <v>0.9931911826133728</v>
       </c>
       <c r="AA21" t="n">
-        <v>77.63624800012467</v>
+        <v>41.7625386664208</v>
       </c>
       <c r="AB21" t="n">
-        <v>16.88696678648606</v>
+        <v>16.88696678648604</v>
       </c>
       <c r="AC21" t="n">
         <v>0.9946804642677307</v>
       </c>
       <c r="AD21" t="n">
-        <v>81.83665174119017</v>
+        <v>45.9629424074863</v>
       </c>
       <c r="AE21" t="n">
-        <v>9.617647211602417</v>
+        <v>9.617647211602394</v>
       </c>
       <c r="AF21" t="n">
         <v>0.9729381799697876</v>
       </c>
       <c r="AG21" t="n">
-        <v>68.95618844539561</v>
+        <v>33.08247911169174</v>
       </c>
       <c r="AH21" t="n">
-        <v>8.360014570520292</v>
+        <v>8.36001457052028</v>
       </c>
       <c r="AI21" t="n">
         <v>0.9984990358352661</v>
       </c>
       <c r="AJ21" t="n">
-        <v>74.37637816084192</v>
+        <v>38.50266882713805</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.1890791223404449</v>
+        <v>0.1890791223404255</v>
       </c>
       <c r="AL21" t="n">
         <v>0.9942721128463745</v>
       </c>
       <c r="AM21" t="n">
-        <v>66.39966761812251</v>
+        <v>30.52595828441864</v>
       </c>
       <c r="AN21" t="n">
         <v>17.13924002140126</v>
@@ -4685,7 +4685,7 @@
         <v>0.9991348385810852</v>
       </c>
       <c r="AP21" t="n">
-        <v>38.07089379493227</v>
+        <v>2.197184461228396</v>
       </c>
       <c r="AQ21" t="n">
         <v>15.15657140853557</v>
@@ -4694,70 +4694,70 @@
         <v>0.7855234146118164</v>
       </c>
       <c r="AS21" t="n">
-        <v>17.64716493322494</v>
+        <v>-18.22654440047893</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.204329470370681</v>
+        <v>3.204329470370678</v>
       </c>
       <c r="AU21" t="n">
         <v>0.402049720287323</v>
       </c>
       <c r="AV21" t="n">
-        <v>62.0183086390921</v>
+        <v>-0.1752609902239897</v>
       </c>
       <c r="AW21" t="n">
-        <v>65.55616327378678</v>
+        <v>0.0487388448512327</v>
       </c>
       <c r="AX21" t="n">
+        <v>0.193052088960691</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.2269988364361737</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.3657401876246666</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-0.1274595869348403</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.6147344061668889</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.3097148651772379</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.4551623729949341</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.3707013231642691</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>62.01830863909207</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>65.55616327378675</v>
+      </c>
+      <c r="BH21" t="n">
         <v>127.5399963175865</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>-0.1752609902239897</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.0487388448512327</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0.193052088960691</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0.2269988364361737</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0.3657401876246666</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>-0.1274595869348403</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0.6147344061668889</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0.3097148651772379</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0.4551623729949341</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0.3707013231642691</v>
       </c>
       <c r="BI21" t="n">
         <v>0.6205030395592672</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.6006226901338234</v>
+        <v>0.6006226901338341</v>
       </c>
       <c r="BK21" t="n">
-        <v>-0.7771561212346185</v>
+        <v>-0.7771561212346398</v>
       </c>
       <c r="BL21" t="n">
-        <v>3.343439304039013</v>
+        <v>3.343439304039038</v>
       </c>
       <c r="BM21" t="n">
-        <v>2.106298483389608</v>
+        <v>2.106298483389594</v>
       </c>
       <c r="BN21" t="n">
-        <v>3.125707763345652</v>
+        <v>3.125707763345623</v>
       </c>
     </row>
     <row r="22">
@@ -4768,115 +4768,115 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>157.8396249324718</v>
+        <v>121.9659155987679</v>
       </c>
       <c r="D22" t="n">
-        <v>5.579571013754986</v>
+        <v>5.579571013754987</v>
       </c>
       <c r="E22" t="n">
         <v>0.9996491670608521</v>
       </c>
       <c r="F22" t="n">
-        <v>141.436361759267</v>
+        <v>105.5626524255631</v>
       </c>
       <c r="G22" t="n">
-        <v>15.56016637923869</v>
+        <v>15.5601663792387</v>
       </c>
       <c r="H22" t="n">
         <v>0.9999518394470215</v>
       </c>
       <c r="I22" t="n">
-        <v>136.1355314863489</v>
+        <v>100.2618221526451</v>
       </c>
       <c r="J22" t="n">
-        <v>1.689196647481708</v>
+        <v>1.689196647481715</v>
       </c>
       <c r="K22" t="n">
         <v>0.9992794394493103</v>
       </c>
       <c r="L22" t="n">
-        <v>131.3579153507314</v>
+        <v>95.48420601702752</v>
       </c>
       <c r="M22" t="n">
-        <v>3.818171075049861</v>
+        <v>3.818171075049867</v>
       </c>
       <c r="N22" t="n">
         <v>0.999037504196167</v>
       </c>
       <c r="O22" t="n">
-        <v>122.5087023795919</v>
+        <v>86.63499304588805</v>
       </c>
       <c r="P22" t="n">
-        <v>10.3398911496426</v>
+        <v>10.33989114964262</v>
       </c>
       <c r="Q22" t="n">
         <v>0.984257698059082</v>
       </c>
       <c r="R22" t="n">
-        <v>130.2354285057555</v>
+        <v>94.36171917205162</v>
       </c>
       <c r="S22" t="n">
-        <v>15.74758976063828</v>
+        <v>15.7475897606383</v>
       </c>
       <c r="T22" t="n">
         <v>0.994414210319519</v>
       </c>
       <c r="U22" t="n">
-        <v>126.7037087298454</v>
+        <v>90.82999939614155</v>
       </c>
       <c r="V22" t="n">
-        <v>24.31559461228389</v>
+        <v>24.31559461228391</v>
       </c>
       <c r="W22" t="n">
         <v>0.9917260408401489</v>
       </c>
       <c r="X22" t="n">
-        <v>81.79953554843335</v>
+        <v>45.92582621472948</v>
       </c>
       <c r="Y22" t="n">
-        <v>25.39145287047043</v>
+        <v>25.39145287047041</v>
       </c>
       <c r="Z22" t="n">
         <v>0.9922822117805481</v>
       </c>
       <c r="AA22" t="n">
-        <v>78.60626058375583</v>
+        <v>42.73255125005196</v>
       </c>
       <c r="AB22" t="n">
-        <v>17.71853832488364</v>
+        <v>17.71853832488365</v>
       </c>
       <c r="AC22" t="n">
         <v>0.9927927255630493</v>
       </c>
       <c r="AD22" t="n">
-        <v>81.92285578301613</v>
+        <v>46.04914644931226</v>
       </c>
       <c r="AE22" t="n">
-        <v>9.760349354845431</v>
+        <v>9.760349354845413</v>
       </c>
       <c r="AF22" t="n">
         <v>0.9606408476829529</v>
       </c>
       <c r="AG22" t="n">
-        <v>69.14965852778009</v>
+        <v>33.27594919407622</v>
       </c>
       <c r="AH22" t="n">
-        <v>9.149754301030583</v>
+        <v>9.149754301030585</v>
       </c>
       <c r="AI22" t="n">
         <v>0.9991849064826965</v>
       </c>
       <c r="AJ22" t="n">
-        <v>74.1532102544257</v>
+        <v>38.27950092072183</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.7062546750332501</v>
+        <v>0.7062546750332447</v>
       </c>
       <c r="AL22" t="n">
         <v>0.9970007538795471</v>
       </c>
       <c r="AM22" t="n">
-        <v>67.53011257090468</v>
+        <v>31.65640323720081</v>
       </c>
       <c r="AN22" t="n">
         <v>17.93941741294049</v>
@@ -4885,79 +4885,79 @@
         <v>0.9994481205940247</v>
       </c>
       <c r="AP22" t="n">
-        <v>39.03338249693526</v>
+        <v>3.159673163231389</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15.14938029837103</v>
+        <v>15.14938029837101</v>
       </c>
       <c r="AR22" t="n">
         <v>0.8171294927597046</v>
       </c>
       <c r="AS22" t="n">
-        <v>20.9355983328312</v>
+        <v>-14.93811100087267</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.865213597074472</v>
+        <v>3.865213597074468</v>
       </c>
       <c r="AU22" t="n">
         <v>0.4327878654003143</v>
       </c>
       <c r="AV22" t="n">
-        <v>62.08616753672923</v>
+        <v>-0.1783533299222881</v>
       </c>
       <c r="AW22" t="n">
+        <v>0.06423300885139938</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.5508219942133508</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.2723754720484948</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.2388933871654757</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.0294117217368246</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.066451377057014</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.09836846209586625</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.179829049617688</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0.4068922489247377</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>62.08616753672916</v>
+      </c>
+      <c r="BG22" t="n">
         <v>70.11276185758688</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="BH22" t="n">
         <v>134.7800884915475</v>
       </c>
-      <c r="AY22" t="n">
-        <v>-0.1783533299222881</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0.06423300885139938</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0.5508219942133508</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0.2723754720484948</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0.2388933871654757</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0.0294117217368246</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.066451377057014</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0.09836846209586625</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.179829049617688</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0.4068922489247377</v>
-      </c>
       <c r="BI22" t="n">
-        <v>2.127933845054599</v>
+        <v>2.127933845054606</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.9199105080510446</v>
+        <v>0.9199105080510463</v>
       </c>
       <c r="BK22" t="n">
-        <v>3.779725115902615</v>
+        <v>3.779725115902643</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.2059813715983267</v>
+        <v>0.2059813715983196</v>
       </c>
       <c r="BM22" t="n">
-        <v>5.114542668193423</v>
+        <v>5.114542668193408</v>
       </c>
       <c r="BN22" t="n">
-        <v>-1.233754100043456</v>
+        <v>-1.233754100043441</v>
       </c>
     </row>
     <row r="23">
@@ -4968,70 +4968,70 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>159.0474230177859</v>
+        <v>123.173713684082</v>
       </c>
       <c r="D23" t="n">
-        <v>5.089065876412889</v>
+        <v>5.089065876412899</v>
       </c>
       <c r="E23" t="n">
         <v>0.9997445940971375</v>
       </c>
       <c r="F23" t="n">
-        <v>142.511489543509</v>
+        <v>106.6377802098051</v>
       </c>
       <c r="G23" t="n">
-        <v>14.65402156748669</v>
+        <v>14.6540215674867</v>
       </c>
       <c r="H23" t="n">
         <v>0.9998051524162292</v>
       </c>
       <c r="I23" t="n">
-        <v>135.8932170462101</v>
+        <v>100.0195077125062</v>
       </c>
       <c r="J23" t="n">
-        <v>1.431306879571139</v>
+        <v>1.431306879571144</v>
       </c>
       <c r="K23" t="n">
         <v>0.999442994594574</v>
       </c>
       <c r="L23" t="n">
-        <v>131.679867683573</v>
+        <v>95.80615834986911</v>
       </c>
       <c r="M23" t="n">
-        <v>3.883670238738347</v>
+        <v>3.883670238738365</v>
       </c>
       <c r="N23" t="n">
         <v>0.9994041919708252</v>
       </c>
       <c r="O23" t="n">
-        <v>123.0555676399393</v>
+        <v>87.18185830623547</v>
       </c>
       <c r="P23" t="n">
-        <v>9.961392017121</v>
+        <v>9.96139201712101</v>
       </c>
       <c r="Q23" t="n">
         <v>0.9810127019882202</v>
       </c>
       <c r="R23" t="n">
-        <v>130.7597383539728</v>
+        <v>94.88602902026888</v>
       </c>
       <c r="S23" t="n">
-        <v>15.33128454330119</v>
+        <v>15.3312845433012</v>
       </c>
       <c r="T23" t="n">
         <v>0.9946574568748474</v>
       </c>
       <c r="U23" t="n">
-        <v>127.4881971643326</v>
+        <v>91.61448783062875</v>
       </c>
       <c r="V23" t="n">
-        <v>23.89073473341921</v>
+        <v>23.89073473341922</v>
       </c>
       <c r="W23" t="n">
         <v>0.9892247319221497</v>
       </c>
       <c r="X23" t="n">
-        <v>83.34440677723987</v>
+        <v>47.470697443536</v>
       </c>
       <c r="Y23" t="n">
         <v>25.70532129165974</v>
@@ -5040,52 +5040,52 @@
         <v>0.9859248995780945</v>
       </c>
       <c r="AA23" t="n">
-        <v>79.76915075423869</v>
+        <v>43.89544142053482</v>
       </c>
       <c r="AB23" t="n">
-        <v>17.97089272357047</v>
+        <v>17.97089272357048</v>
       </c>
       <c r="AC23" t="n">
         <v>0.9867681860923767</v>
       </c>
       <c r="AD23" t="n">
-        <v>82.31443851552112</v>
+        <v>46.44072918181725</v>
       </c>
       <c r="AE23" t="n">
-        <v>9.859823673329458</v>
+        <v>9.859823673329455</v>
       </c>
       <c r="AF23" t="n">
         <v>0.9702966809272766</v>
       </c>
       <c r="AG23" t="n">
-        <v>70.05783243382231</v>
+        <v>34.18412310011844</v>
       </c>
       <c r="AH23" t="n">
-        <v>9.744798376205125</v>
+        <v>9.74479837620512</v>
       </c>
       <c r="AI23" t="n">
         <v>0.9993143081665039</v>
       </c>
       <c r="AJ23" t="n">
-        <v>74.01967150099735</v>
+        <v>38.14596216729348</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.9553787556100417</v>
+        <v>0.9553787556100399</v>
       </c>
       <c r="AL23" t="n">
         <v>0.9984355568885803</v>
       </c>
       <c r="AM23" t="n">
-        <v>68.15455010596743</v>
+        <v>32.28084077226356</v>
       </c>
       <c r="AN23" t="n">
-        <v>18.47641315866025</v>
+        <v>18.47641315866024</v>
       </c>
       <c r="AO23" t="n">
         <v>0.9998520612716675</v>
       </c>
       <c r="AP23" t="n">
-        <v>39.04260675957863</v>
+        <v>3.168897425874754</v>
       </c>
       <c r="AQ23" t="n">
         <v>15.21397042781749</v>
@@ -5094,70 +5094,70 @@
         <v>0.6574376225471497</v>
       </c>
       <c r="AS23" t="n">
-        <v>24.08875810339096</v>
+        <v>-11.78495123031291</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.501145383144944</v>
+        <v>3.501145383144947</v>
       </c>
       <c r="AU23" t="n">
         <v>0.1759843528270721</v>
       </c>
       <c r="AV23" t="n">
-        <v>66.2741763292013</v>
+        <v>-0.04679497252119091</v>
       </c>
       <c r="AW23" t="n">
-        <v>73.11561350559201</v>
+        <v>0.07958310715695305</v>
       </c>
       <c r="AX23" t="n">
+        <v>0.7378030330576806</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.03240057762632631</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.4245636310983159</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0.1523220792729809</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.8114713303586214</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>-0.3219117509557812</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.26894687084441</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>-0.08681277011303479</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>66.27417632920128</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>73.11561350559204</v>
+      </c>
+      <c r="BH23" t="n">
         <v>137.7690816539734</v>
       </c>
-      <c r="AY23" t="n">
-        <v>-0.04679497252119091</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0.07958310715695305</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0.7378030330576806</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0.03240057762632631</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0.4245636310983159</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0.1523220792729809</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0.8114713303586214</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>-0.3219117509557812</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.26894687084441</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>-0.08681277011303479</v>
-      </c>
       <c r="BI23" t="n">
-        <v>2.460324055661356</v>
+        <v>2.46032405566136</v>
       </c>
       <c r="BJ23" t="n">
-        <v>-0.6107795680626431</v>
+        <v>-0.6107795680626644</v>
       </c>
       <c r="BK23" t="n">
-        <v>-0.365193378037965</v>
+        <v>-0.3651933780380006</v>
       </c>
       <c r="BL23" t="n">
-        <v>-3.989786090956279</v>
+        <v>-3.989786090956319</v>
       </c>
       <c r="BM23" t="n">
-        <v>-0.361209716697303</v>
+        <v>-0.3612097166972887</v>
       </c>
       <c r="BN23" t="n">
-        <v>-4.75658329309244</v>
+        <v>-4.756583293092419</v>
       </c>
     </row>
     <row r="24">
@@ -5168,70 +5168,70 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>160.4322879872424</v>
+        <v>124.5585786535385</v>
       </c>
       <c r="D24" t="n">
-        <v>4.984948990192805</v>
+        <v>4.984948990192819</v>
       </c>
       <c r="E24" t="n">
         <v>0.9987649917602539</v>
       </c>
       <c r="F24" t="n">
-        <v>143.7439127171293</v>
+        <v>107.8702033834254</v>
       </c>
       <c r="G24" t="n">
-        <v>14.65082371488529</v>
+        <v>14.65082371488531</v>
       </c>
       <c r="H24" t="n">
         <v>0.999738872051239</v>
       </c>
       <c r="I24" t="n">
-        <v>136.0923685926072</v>
+        <v>100.2186592589033</v>
       </c>
       <c r="J24" t="n">
-        <v>1.795618584815486</v>
+        <v>1.795618584815492</v>
       </c>
       <c r="K24" t="n">
         <v>0.9991142153739929</v>
       </c>
       <c r="L24" t="n">
-        <v>131.6150827610746</v>
+        <v>95.74137342737076</v>
       </c>
       <c r="M24" t="n">
-        <v>3.881040532538208</v>
+        <v>3.881040532538232</v>
       </c>
       <c r="N24" t="n">
         <v>0.9990624785423279</v>
       </c>
       <c r="O24" t="n">
-        <v>123.8317124387051</v>
+        <v>87.95800310500125</v>
       </c>
       <c r="P24" t="n">
-        <v>10.58252212849067</v>
+        <v>10.58252212849069</v>
       </c>
       <c r="Q24" t="n">
         <v>0.9882760643959045</v>
       </c>
       <c r="R24" t="n">
-        <v>131.9381957358502</v>
+        <v>96.06448640214636</v>
       </c>
       <c r="S24" t="n">
-        <v>15.25891892453456</v>
+        <v>15.25891892453457</v>
       </c>
       <c r="T24" t="n">
         <v>0.9921106696128845</v>
       </c>
       <c r="U24" t="n">
-        <v>128.5085881010015</v>
+        <v>92.63487876729762</v>
       </c>
       <c r="V24" t="n">
-        <v>23.54836971201794</v>
+        <v>23.54836971201795</v>
       </c>
       <c r="W24" t="n">
         <v>0.9906127452850342</v>
       </c>
       <c r="X24" t="n">
-        <v>84.33742929012217</v>
+        <v>48.4637199564183</v>
       </c>
       <c r="Y24" t="n">
         <v>25.47281955150848</v>
@@ -5240,52 +5240,52 @@
         <v>0.9885718822479248</v>
       </c>
       <c r="AA24" t="n">
-        <v>80.22920324447307</v>
+        <v>44.3554939107692</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.93419046604888</v>
+        <v>17.93419046604887</v>
       </c>
       <c r="AC24" t="n">
         <v>0.9873629808425903</v>
       </c>
       <c r="AD24" t="n">
-        <v>82.77198304521276</v>
+        <v>46.89827371150889</v>
       </c>
       <c r="AE24" t="n">
-        <v>9.79721393991025</v>
+        <v>9.79721393991024</v>
       </c>
       <c r="AF24" t="n">
         <v>0.9700224995613098</v>
       </c>
       <c r="AG24" t="n">
-        <v>70.62526459389545</v>
+        <v>34.75155526019158</v>
       </c>
       <c r="AH24" t="n">
-        <v>10.48988179957612</v>
+        <v>10.48988179957613</v>
       </c>
       <c r="AI24" t="n">
         <v>0.9992142915725708</v>
       </c>
       <c r="AJ24" t="n">
-        <v>74.05962030938332</v>
+        <v>38.18591097567945</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.9135956459857084</v>
+        <v>0.9135956459857049</v>
       </c>
       <c r="AL24" t="n">
         <v>0.9982661604881287</v>
       </c>
       <c r="AM24" t="n">
-        <v>69.3515696424119</v>
+        <v>33.47786030870803</v>
       </c>
       <c r="AN24" t="n">
-        <v>18.81077543218086</v>
+        <v>18.81077543218085</v>
       </c>
       <c r="AO24" t="n">
         <v>0.9999135732650757</v>
       </c>
       <c r="AP24" t="n">
-        <v>42.49178297976231</v>
+        <v>6.618073646058434</v>
       </c>
       <c r="AQ24" t="n">
         <v>15.61452987346243</v>
@@ -5294,70 +5294,70 @@
         <v>0.7602368593215942</v>
       </c>
       <c r="AS24" t="n">
-        <v>26.38357649458216</v>
+        <v>-9.490132839121713</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.578234733419208</v>
+        <v>3.578234733419216</v>
       </c>
       <c r="AU24" t="n">
         <v>0.5948168635368347</v>
       </c>
       <c r="AV24" t="n">
-        <v>67.00681564805194</v>
+        <v>-0.01918711560838204</v>
       </c>
       <c r="AW24" t="n">
-        <v>69.38237510151095</v>
+        <v>0.02030108837371003</v>
       </c>
       <c r="AX24" t="n">
+        <v>0.6156231494660034</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>-0.1420041348071805</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.5435375457114375</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.112973882796922</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0.4226278751454515</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.1633887595318768</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.006203509391618</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>-0.008593214319102316</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>67.00681564805188</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>69.38237510151087</v>
+      </c>
+      <c r="BH24" t="n">
         <v>134.0576690581529</v>
       </c>
-      <c r="AY24" t="n">
-        <v>-0.01918711560838204</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0.02030108837371003</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0.6156231494660034</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>-0.1420041348071805</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>0.5435375457114375</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>0.112973882796922</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>0.4226278751454515</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>0.1633887595318768</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.006203509391618</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>-0.008593214319102316</v>
-      </c>
       <c r="BI24" t="n">
-        <v>0.906374708929313</v>
+        <v>0.9063747089292775</v>
       </c>
       <c r="BJ24" t="n">
-        <v>-0.842779243140809</v>
+        <v>-0.8427792431407859</v>
       </c>
       <c r="BK24" t="n">
-        <v>-4.199847066009944</v>
+        <v>-4.199847066009994</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.815730181756301</v>
+        <v>0.81573018175634</v>
       </c>
       <c r="BM24" t="n">
-        <v>-4.398623917991458</v>
+        <v>-4.398623917991429</v>
       </c>
       <c r="BN24" t="n">
-        <v>1.419297706146253</v>
+        <v>1.419297706146232</v>
       </c>
     </row>
     <row r="25">
@@ -5368,16 +5368,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>161.8271361006067</v>
+        <v>125.9534267669029</v>
       </c>
       <c r="D25" t="n">
-        <v>5.248439058344417</v>
+        <v>5.248439058344415</v>
       </c>
       <c r="E25" t="n">
         <v>0.999562680721283</v>
       </c>
       <c r="F25" t="n">
-        <v>144.7442075039478</v>
+        <v>108.8704981702439</v>
       </c>
       <c r="G25" t="n">
         <v>15.10715890437999</v>
@@ -5386,34 +5386,34 @@
         <v>0.9998762607574463</v>
       </c>
       <c r="I25" t="n">
-        <v>136.1932795098487</v>
+        <v>100.3195701761449</v>
       </c>
       <c r="J25" t="n">
-        <v>2.111037234042556</v>
+        <v>2.111037234042553</v>
       </c>
       <c r="K25" t="n">
         <v>0.999142050743103</v>
       </c>
       <c r="L25" t="n">
-        <v>132.0240426570811</v>
+        <v>96.15033332337724</v>
       </c>
       <c r="M25" t="n">
-        <v>4.244751625872681</v>
+        <v>4.244751625872673</v>
       </c>
       <c r="N25" t="n">
         <v>0.9996168613433838</v>
       </c>
       <c r="O25" t="n">
-        <v>124.790362094311</v>
+        <v>88.91665276060714</v>
       </c>
       <c r="P25" t="n">
-        <v>11.20047062001331</v>
+        <v>11.2004706200133</v>
       </c>
       <c r="Q25" t="n">
         <v>0.989474356174469</v>
       </c>
       <c r="R25" t="n">
-        <v>133.1044785519864</v>
+        <v>97.2307692182825</v>
       </c>
       <c r="S25" t="n">
         <v>15.75349848321144</v>
@@ -5422,7 +5422,7 @@
         <v>0.9943594336509705</v>
       </c>
       <c r="U25" t="n">
-        <v>129.9283291431184</v>
+        <v>94.05461980941449</v>
       </c>
       <c r="V25" t="n">
         <v>24.23379776325632</v>
@@ -5431,7 +5431,7 @@
         <v>0.9881227612495422</v>
       </c>
       <c r="X25" t="n">
-        <v>85.3568137960231</v>
+        <v>49.48310446231923</v>
       </c>
       <c r="Y25" t="n">
         <v>25.34887435588431</v>
@@ -5440,25 +5440,25 @@
         <v>0.9889642000198364</v>
       </c>
       <c r="AA25" t="n">
-        <v>80.6144065045296</v>
+        <v>44.74069717082573</v>
       </c>
       <c r="AB25" t="n">
-        <v>17.96027650224403</v>
+        <v>17.96027650224402</v>
       </c>
       <c r="AC25" t="n">
         <v>0.9965711832046509</v>
       </c>
       <c r="AD25" t="n">
-        <v>83.40151360694399</v>
+        <v>47.52780427324012</v>
       </c>
       <c r="AE25" t="n">
-        <v>9.549388479679209</v>
+        <v>9.549388479679189</v>
       </c>
       <c r="AF25" t="n">
         <v>0.9662514925003052</v>
       </c>
       <c r="AG25" t="n">
-        <v>71.28907873275432</v>
+        <v>35.41536939905045</v>
       </c>
       <c r="AH25" t="n">
         <v>11.02598474380818</v>
@@ -5467,97 +5467,97 @@
         <v>0.9989643096923828</v>
       </c>
       <c r="AJ25" t="n">
-        <v>73.98129726978058</v>
+        <v>38.10758793607671</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.9521809030086388</v>
+        <v>0.9521809030086437</v>
       </c>
       <c r="AL25" t="n">
         <v>0.9991223216056824</v>
       </c>
       <c r="AM25" t="n">
-        <v>70.29932711986785</v>
+        <v>34.42561778616398</v>
       </c>
       <c r="AN25" t="n">
-        <v>19.37772060962433</v>
+        <v>19.37772060962434</v>
       </c>
       <c r="AO25" t="n">
         <v>0.9991262555122375</v>
       </c>
       <c r="AP25" t="n">
-        <v>43.19053406411029</v>
+        <v>7.316824730406417</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15.45815975108047</v>
+        <v>15.45815975108045</v>
       </c>
       <c r="AR25" t="n">
         <v>0.8831926584243774</v>
       </c>
       <c r="AS25" t="n">
-        <v>28.28060921202315</v>
+        <v>-7.593100121680724</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.315978354596098</v>
+        <v>3.315978354596077</v>
       </c>
       <c r="AU25" t="n">
         <v>0.3285631537437439</v>
       </c>
       <c r="AV25" t="n">
-        <v>68.08692574705992</v>
+        <v>-0.006192795773770854</v>
       </c>
       <c r="AW25" t="n">
-        <v>64.71591937357212</v>
+        <v>0.04256228183178834</v>
       </c>
       <c r="AX25" t="n">
-        <v>128.9718338179904</v>
+        <v>0.4537947634433195</v>
       </c>
       <c r="AY25" t="n">
-        <v>-0.006192795773770854</v>
+        <v>-0.1859238807191161</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.04256228183178834</v>
+        <v>0.6505113966921598</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.4537947634433195</v>
+        <v>0.06397734297082636</v>
       </c>
       <c r="BB25" t="n">
-        <v>-0.1859238807191161</v>
+        <v>1.138248849422375</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.6505113966921598</v>
+        <v>0.7343332818213852</v>
       </c>
       <c r="BD25" t="n">
-        <v>0.06397734297082636</v>
+        <v>1.251760442206205</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.138248849422375</v>
+        <v>0.2389664345599307</v>
       </c>
       <c r="BF25" t="n">
-        <v>0.7343332818213852</v>
+        <v>68.08692574705984</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.251760442206205</v>
+        <v>64.71591937357205</v>
       </c>
       <c r="BH25" t="n">
-        <v>0.2389664345599307</v>
+        <v>128.9718338179905</v>
       </c>
       <c r="BI25" t="n">
-        <v>0.7747655693797384</v>
+        <v>0.7747655693797881</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-0.218476834588909</v>
+        <v>-0.2184768345888273</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.266266985474637</v>
+        <v>1.26626698547468</v>
       </c>
       <c r="BL25" t="n">
-        <v>5.699418382449021</v>
+        <v>5.699418382449089</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.477385695595203</v>
+        <v>2.477385695595174</v>
       </c>
       <c r="BN25" t="n">
-        <v>7.219615274672144</v>
+        <v>7.219615274672087</v>
       </c>
     </row>
     <row r="26">
@@ -5568,52 +5568,52 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>162.8635325330369</v>
+        <v>126.989823199333</v>
       </c>
       <c r="D26" t="n">
-        <v>5.067687338971098</v>
+        <v>5.067687338971077</v>
       </c>
       <c r="E26" t="n">
         <v>0.9996787309646606</v>
       </c>
       <c r="F26" t="n">
-        <v>146.2183039239112</v>
+        <v>110.3445945902074</v>
       </c>
       <c r="G26" t="n">
-        <v>14.71211859520446</v>
+        <v>14.71211859520445</v>
       </c>
       <c r="H26" t="n">
         <v>0.9997664093971252</v>
       </c>
       <c r="I26" t="n">
-        <v>136.1573970064204</v>
+        <v>100.2836876727165</v>
       </c>
       <c r="J26" t="n">
-        <v>2.18895445478725</v>
+        <v>2.188954454787234</v>
       </c>
       <c r="K26" t="n">
         <v>0.9991629123687744</v>
       </c>
       <c r="L26" t="n">
-        <v>131.9279285187417</v>
+        <v>96.05421918503784</v>
       </c>
       <c r="M26" t="n">
-        <v>3.964265863946139</v>
+        <v>3.964265863946144</v>
       </c>
       <c r="N26" t="n">
         <v>0.9996237754821777</v>
       </c>
       <c r="O26" t="n">
-        <v>125.7566736099568</v>
+        <v>89.88296427625292</v>
       </c>
       <c r="P26" t="n">
-        <v>11.483537389877</v>
+        <v>11.48353738987699</v>
       </c>
       <c r="Q26" t="n">
         <v>0.9866771697998047</v>
       </c>
       <c r="R26" t="n">
-        <v>134.2709967430602</v>
+        <v>98.39728740935631</v>
       </c>
       <c r="S26" t="n">
         <v>15.86112164436503</v>
@@ -5622,70 +5622,70 @@
         <v>0.9927845001220703</v>
       </c>
       <c r="U26" t="n">
-        <v>131.233807827564</v>
+        <v>95.36009849386012</v>
       </c>
       <c r="V26" t="n">
-        <v>24.24548534636804</v>
+        <v>24.24548534636802</v>
       </c>
       <c r="W26" t="n">
         <v>0.9887056946754456</v>
       </c>
       <c r="X26" t="n">
-        <v>86.84095017453458</v>
+        <v>50.96724084083071</v>
       </c>
       <c r="Y26" t="n">
-        <v>25.18185554666721</v>
+        <v>25.18185554666722</v>
       </c>
       <c r="Z26" t="n">
         <v>0.9893559813499451</v>
       </c>
       <c r="AA26" t="n">
-        <v>82.50570094331782</v>
+        <v>46.63199160961395</v>
       </c>
       <c r="AB26" t="n">
-        <v>17.86890232816654</v>
+        <v>17.86890232816656</v>
       </c>
       <c r="AC26" t="n">
         <v>0.9955537915229797</v>
       </c>
       <c r="AD26" t="n">
-        <v>84.07300583859708</v>
+        <v>48.19929650489321</v>
       </c>
       <c r="AE26" t="n">
-        <v>9.267912519739014</v>
+        <v>9.26791251973903</v>
       </c>
       <c r="AF26" t="n">
         <v>0.9312916994094849</v>
       </c>
       <c r="AG26" t="n">
-        <v>71.53285412078209</v>
+        <v>35.65914478707822</v>
       </c>
       <c r="AH26" t="n">
-        <v>10.97628005007479</v>
+        <v>10.9762800500748</v>
       </c>
       <c r="AI26" t="n">
         <v>0.9968852400779724</v>
       </c>
       <c r="AJ26" t="n">
-        <v>74.04723471783578</v>
+        <v>38.17352538413191</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.6508360517785832</v>
+        <v>0.6508360517785905</v>
       </c>
       <c r="AL26" t="n">
         <v>0.9994354844093323</v>
       </c>
       <c r="AM26" t="n">
-        <v>71.26709146702544</v>
+        <v>35.39338213332157</v>
       </c>
       <c r="AN26" t="n">
-        <v>18.95079917096078</v>
+        <v>18.95079917096077</v>
       </c>
       <c r="AO26" t="n">
         <v>0.999708354473114</v>
       </c>
       <c r="AP26" t="n">
-        <v>42.73585461555643</v>
+        <v>6.862145281852563</v>
       </c>
       <c r="AQ26" t="n">
         <v>14.17484689266124</v>
@@ -5694,70 +5694,70 @@
         <v>0.8411703109741211</v>
       </c>
       <c r="AS26" t="n">
-        <v>30.62710660569211</v>
+        <v>-5.246602728011759</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.015331511801861</v>
+        <v>3.015331511801862</v>
       </c>
       <c r="AU26" t="n">
         <v>0.217385545372963</v>
       </c>
       <c r="AV26" t="n">
-        <v>68.55634678681142</v>
+        <v>0.06593744805519464</v>
       </c>
       <c r="AW26" t="n">
-        <v>71.91490907246022</v>
+        <v>0.07213024382896549</v>
       </c>
       <c r="AX26" t="n">
-        <v>139.0124404493433</v>
+        <v>0.2437753880277711</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.06593744805519464</v>
+        <v>-0.2100193754155484</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.07213024382896549</v>
+        <v>0.6714922316530902</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.2437753880277711</v>
+        <v>0.02098083496093039</v>
       </c>
       <c r="BB26" t="n">
-        <v>-0.2100193754155484</v>
+        <v>1.891294438788222</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.6714922316530902</v>
+        <v>0.753045589365847</v>
       </c>
       <c r="BD26" t="n">
-        <v>0.02098083496093039</v>
+        <v>1.484136378511479</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.891294438788222</v>
+        <v>0.2323759363052744</v>
       </c>
       <c r="BF26" t="n">
-        <v>0.753045589365847</v>
+        <v>68.55634678681146</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.484136378511479</v>
+        <v>71.91490907246023</v>
       </c>
       <c r="BH26" t="n">
-        <v>0.2323759363052744</v>
+        <v>139.0124404493432</v>
       </c>
       <c r="BI26" t="n">
-        <v>0.4694210397514951</v>
+        <v>0.469421039751623</v>
       </c>
       <c r="BJ26" t="n">
-        <v>-0.3053445296282433</v>
+        <v>-0.3053445296281652</v>
       </c>
       <c r="BK26" t="n">
-        <v>7.198989698888099</v>
+        <v>7.198989698888184</v>
       </c>
       <c r="BL26" t="n">
-        <v>5.932722713413462</v>
+        <v>5.932722713413504</v>
       </c>
       <c r="BM26" t="n">
-        <v>10.04060663135283</v>
+        <v>10.04060663135274</v>
       </c>
       <c r="BN26" t="n">
-        <v>7.563220935757627</v>
+        <v>7.56322093575757</v>
       </c>
     </row>
   </sheetData>
